--- a/SIM Sheet v0.6-Duchy of Warsaw Sim 204.xlsx
+++ b/SIM Sheet v0.6-Duchy of Warsaw Sim 204.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ec1d83f1b5dc1320/Υπολογιστής/AU/new AUSTERLITZ new/124-W424/2-1813-424-W/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\AuSimBattle\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="451" documentId="13_ncr:1_{E84C0A5B-B8D5-407B-9016-E181C7BA516E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{23F5C49B-4106-4380-880E-A7481DC2A95F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{505BACA5-B41A-43C6-8B05-D86ABA63BB95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4290" yWindow="1530" windowWidth="28695" windowHeight="20070" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,9 +36,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="29">
   <si>
     <t>State:</t>
-  </si>
-  <si>
-    <t>Choose</t>
   </si>
   <si>
     <t>Game:</t>
@@ -119,16 +116,16 @@
     <t>Army B</t>
   </si>
   <si>
-    <t>CHRISTOS KARAS</t>
+    <t>W</t>
+  </si>
+  <si>
+    <t>TEST AU SIM</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-  </numFmts>
   <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -569,7 +566,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -695,12 +692,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -710,20 +718,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Κανονικό" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
     <dxf>
@@ -990,29 +987,29 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AO123"/>
-  <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.109375" customWidth="1"/>
-    <col min="2" max="8" width="8.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" customWidth="1"/>
-    <col min="10" max="11" width="8.6640625" customWidth="1"/>
-    <col min="12" max="12" width="10.109375" customWidth="1"/>
-    <col min="13" max="13" width="8.6640625" customWidth="1"/>
+    <col min="1" max="1" width="3.140625" customWidth="1"/>
+    <col min="2" max="8" width="8.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="10" max="11" width="8.7109375" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" customWidth="1"/>
+    <col min="13" max="13" width="8.7109375" customWidth="1"/>
     <col min="14" max="14" width="10" customWidth="1"/>
-    <col min="15" max="16" width="8.6640625" customWidth="1"/>
+    <col min="15" max="16" width="8.7109375" customWidth="1"/>
     <col min="17" max="17" width="10" customWidth="1"/>
-    <col min="18" max="22" width="8.6640625" customWidth="1"/>
+    <col min="18" max="22" width="8.7109375" customWidth="1"/>
     <col min="23" max="23" width="10" customWidth="1"/>
-    <col min="24" max="25" width="8.5546875" customWidth="1"/>
-    <col min="26" max="27" width="20.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.33203125" customWidth="1"/>
-    <col min="29" max="29" width="20.33203125" customWidth="1"/>
-    <col min="30" max="33" width="12.5546875" customWidth="1"/>
-    <col min="34" max="37" width="20.33203125" customWidth="1"/>
-    <col min="38" max="41" width="13.33203125" customWidth="1"/>
+    <col min="24" max="25" width="8.5703125" customWidth="1"/>
+    <col min="26" max="27" width="20.28515625" customWidth="1"/>
+    <col min="28" max="28" width="15.28515625" customWidth="1"/>
+    <col min="29" max="29" width="20.28515625" customWidth="1"/>
+    <col min="30" max="33" width="12.5703125" customWidth="1"/>
+    <col min="34" max="37" width="20.28515625" customWidth="1"/>
+    <col min="38" max="41" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:41" x14ac:dyDescent="0.25">
       <c r="W1" s="1"/>
       <c r="X1" s="1"/>
       <c r="Y1" s="1"/>
@@ -1033,7 +1030,7 @@
       <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
     </row>
-    <row r="2" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
@@ -1059,32 +1056,32 @@
       <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
     </row>
-    <row r="3" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="2"/>
       <c r="B3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="54" t="s">
+      <c r="C3" s="59" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="60"/>
+      <c r="E3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="55"/>
-      <c r="E3" s="2" t="s">
-        <v>2</v>
-      </c>
       <c r="F3" s="3">
-        <v>424</v>
+        <v>123</v>
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="5"/>
       <c r="J3" s="2" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="6">
         <v>204</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R3" s="7">
         <v>70</v>
@@ -1115,16 +1112,16 @@
       <c r="AN3" s="1"/>
       <c r="AO3" s="1"/>
     </row>
-    <row r="4" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6">
+        <v>111333</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="C4" s="6">
-        <v>10008</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>6</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>28</v>
@@ -1132,19 +1129,19 @@
       <c r="G4" s="4"/>
       <c r="H4" s="5"/>
       <c r="J4" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="9">
         <v>46308</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="R4" s="56" t="s">
-        <v>27</v>
-      </c>
-      <c r="S4" s="55"/>
+        <v>7</v>
+      </c>
+      <c r="R4" s="61" t="s">
+        <v>26</v>
+      </c>
+      <c r="S4" s="60"/>
       <c r="W4" s="1"/>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
@@ -1165,7 +1162,7 @@
       <c r="AN4" s="1"/>
       <c r="AO4" s="1"/>
     </row>
-    <row r="5" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="E5" s="2"/>
       <c r="W5" s="1"/>
       <c r="X5" s="1"/>
@@ -1187,9 +1184,9 @@
       <c r="AN5" s="1"/>
       <c r="AO5" s="1"/>
     </row>
-    <row r="6" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="B6" s="8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
@@ -1239,10 +1236,10 @@
       <c r="AN6" s="1"/>
       <c r="AO6" s="1"/>
     </row>
-    <row r="7" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="57" t="str">
+      <c r="E7" s="62" t="str">
         <f>IF(AND(F6="", G6=""), "",
   IF(OR(F6="", G6=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(F6))), NOT(ISNUMBER(VALUE(G6)))), "Error: Coordinates must be numbers",
@@ -1252,7 +1249,7 @@
       </c>
       <c r="F7" s="52"/>
       <c r="G7" s="52"/>
-      <c r="H7" s="57" t="str">
+      <c r="H7" s="62" t="str">
         <f>IF(AND(I6="", J6=""), "",
   IF(OR(I6="", J6=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(I6))), NOT(ISNUMBER(VALUE(J6)))), "Error: Coordinates must be numbers",
@@ -1262,7 +1259,7 @@
       </c>
       <c r="I7" s="52"/>
       <c r="J7" s="52"/>
-      <c r="K7" s="57" t="str">
+      <c r="K7" s="62" t="str">
         <f>IF(AND(L6="", M6=""), "",
   IF(OR(L6="", M6=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(L6))), NOT(ISNUMBER(VALUE(M6)))), "Error: Coordinates must be numbers",
@@ -1272,7 +1269,7 @@
       </c>
       <c r="L7" s="52"/>
       <c r="M7" s="52"/>
-      <c r="N7" s="57" t="str">
+      <c r="N7" s="62" t="str">
         <f>IF(AND(O6="", P6=""), "",
   IF(OR(O6="", P6=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(O6))), NOT(ISNUMBER(VALUE(P6)))), "Error: Coordinates must be numbers",
@@ -1282,7 +1279,7 @@
       </c>
       <c r="O7" s="52"/>
       <c r="P7" s="52"/>
-      <c r="Q7" s="57" t="str">
+      <c r="Q7" s="62" t="str">
         <f>IF(AND(R6="", S6=""), "",
   IF(OR(R6="", S6=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(R6))), NOT(ISNUMBER(VALUE(S6)))), "Error: Coordinates must be numbers",
@@ -1313,7 +1310,7 @@
       <c r="AN7" s="1"/>
       <c r="AO7" s="1"/>
     </row>
-    <row r="8" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="E8" s="13">
         <v>6</v>
       </c>
@@ -1360,8 +1357,8 @@
       <c r="AN8" s="1"/>
       <c r="AO8" s="1"/>
     </row>
-    <row r="9" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="E9" s="57" t="str">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
+      <c r="E9" s="62" t="str">
         <f>IF(AND(F8="", G8=""), "",
   IF(OR(F8="", G8=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(F8))), NOT(ISNUMBER(VALUE(G8)))), "Error: Coordinates must be numbers",
@@ -1371,7 +1368,7 @@
       </c>
       <c r="F9" s="52"/>
       <c r="G9" s="52"/>
-      <c r="H9" s="57" t="str">
+      <c r="H9" s="62" t="str">
         <f>IF(AND(I8="", J8=""), "",
   IF(OR(I8="", J8=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(I8))), NOT(ISNUMBER(VALUE(J8)))), "Error: Coordinates must be numbers",
@@ -1381,7 +1378,7 @@
       </c>
       <c r="I9" s="52"/>
       <c r="J9" s="52"/>
-      <c r="K9" s="57" t="str">
+      <c r="K9" s="62" t="str">
         <f>IF(AND(L8="", M8=""), "",
   IF(OR(L8="", M8=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(L8))), NOT(ISNUMBER(VALUE(M8)))), "Error: Coordinates must be numbers",
@@ -1391,7 +1388,7 @@
       </c>
       <c r="L9" s="52"/>
       <c r="M9" s="52"/>
-      <c r="N9" s="57" t="str">
+      <c r="N9" s="62" t="str">
         <f>IF(AND(O8="", P8=""), "",
   IF(OR(O8="", P8=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(O8))), NOT(ISNUMBER(VALUE(P8)))), "Error: Coordinates must be numbers",
@@ -1401,7 +1398,7 @@
       </c>
       <c r="O9" s="52"/>
       <c r="P9" s="52"/>
-      <c r="Q9" s="57" t="str">
+      <c r="Q9" s="62" t="str">
         <f>IF(AND(R8="", S8=""), "",
   IF(OR(R8="", S8=""), "Error: Both X and Y coordinates must be specified",
     IF(OR(NOT(ISNUMBER(VALUE(R8))), NOT(ISNUMBER(VALUE(S8)))), "Error: Coordinates must be numbers",
@@ -1432,9 +1429,9 @@
       <c r="AN9" s="1"/>
       <c r="AO9" s="1"/>
     </row>
-    <row r="10" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="W10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10" s="1"/>
       <c r="Y10" s="1"/>
@@ -1455,205 +1452,205 @@
       <c r="AN10" s="1"/>
       <c r="AO10" s="1"/>
     </row>
-    <row r="11" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="18"/>
       <c r="B11" s="19"/>
       <c r="C11" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" s="55"/>
+      <c r="E11" s="56"/>
+      <c r="F11" s="20" t="s">
         <v>11</v>
-      </c>
-      <c r="D11" s="58"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="20" t="s">
-        <v>12</v>
       </c>
       <c r="G11" s="20"/>
       <c r="H11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="20"/>
+      <c r="J11" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="J11" s="58" t="s">
+      <c r="K11" s="56"/>
+      <c r="L11" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="K11" s="59"/>
-      <c r="L11" s="58" t="s">
+      <c r="M11" s="57"/>
+      <c r="N11" s="20" t="s">
         <v>15</v>
-      </c>
-      <c r="M11" s="60"/>
-      <c r="N11" s="20" t="s">
-        <v>16</v>
       </c>
       <c r="O11" s="20"/>
       <c r="P11" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="20"/>
+      <c r="R11" s="55" t="s">
         <v>13</v>
       </c>
-      <c r="Q11" s="20"/>
-      <c r="R11" s="58" t="s">
+      <c r="S11" s="56"/>
+      <c r="T11" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="S11" s="59"/>
-      <c r="T11" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="60"/>
+      <c r="U11" s="57"/>
       <c r="V11" s="18"/>
       <c r="W11" s="21"/>
-      <c r="X11" s="61"/>
-      <c r="Y11" s="59"/>
+      <c r="X11" s="58"/>
+      <c r="Y11" s="56"/>
       <c r="Z11" s="22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AA11" s="22"/>
       <c r="AB11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AC11" s="22"/>
+      <c r="AD11" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="AC11" s="22"/>
-      <c r="AD11" s="61" t="s">
+      <c r="AE11" s="56"/>
+      <c r="AF11" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="AE11" s="59"/>
-      <c r="AF11" s="61" t="s">
+      <c r="AG11" s="57"/>
+      <c r="AH11" s="22" t="s">
         <v>15</v>
-      </c>
-      <c r="AG11" s="60"/>
-      <c r="AH11" s="22" t="s">
-        <v>16</v>
       </c>
       <c r="AI11" s="22"/>
       <c r="AJ11" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="AK11" s="22"/>
+      <c r="AL11" s="58" t="s">
         <v>13</v>
       </c>
-      <c r="AK11" s="22"/>
-      <c r="AL11" s="61" t="s">
+      <c r="AM11" s="56"/>
+      <c r="AN11" s="58" t="s">
         <v>14</v>
       </c>
-      <c r="AM11" s="59"/>
-      <c r="AN11" s="61" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="60"/>
+      <c r="AO11" s="57"/>
     </row>
-    <row r="12" spans="1:41" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="18"/>
       <c r="B12" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="24" t="s">
+      <c r="D12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="E12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="F12" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="F12" s="24" t="s">
+      <c r="G12" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="24" t="s">
+      <c r="H12" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="H12" s="24" t="s">
+      <c r="I12" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="24" t="s">
+      <c r="J12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="K12" s="26" t="s">
+        <v>19</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="N12" s="24" t="s">
         <v>24</v>
       </c>
-      <c r="J12" s="25" t="s">
+      <c r="O12" s="24" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="R12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="S12" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="L12" s="25" t="s">
+      <c r="T12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="U12" s="27" t="s">
         <v>19</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="N12" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="O12" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="P12" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q12" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="R12" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="S12" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="T12" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="U12" s="27" t="s">
-        <v>20</v>
       </c>
       <c r="V12" s="18"/>
       <c r="W12" s="28" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="X12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y12" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="Y12" s="30" t="s">
+      <c r="Z12" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="Z12" s="31" t="s">
+      <c r="AA12" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="AA12" s="31" t="s">
+      <c r="AB12" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="AB12" s="31" t="s">
+      <c r="AC12" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="AC12" s="31" t="s">
+      <c r="AD12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AE12" s="30" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AG12" s="32" t="s">
+        <v>19</v>
+      </c>
+      <c r="AH12" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="AD12" s="29" t="s">
+      <c r="AI12" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="AJ12" s="31" t="s">
+        <v>22</v>
+      </c>
+      <c r="AK12" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="AL12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AM12" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="AE12" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AF12" s="29" t="s">
+      <c r="AN12" s="29" t="s">
+        <v>18</v>
+      </c>
+      <c r="AO12" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="AG12" s="32" t="s">
-        <v>20</v>
-      </c>
-      <c r="AH12" s="31" t="s">
-        <v>25</v>
-      </c>
-      <c r="AI12" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="AJ12" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="AK12" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="AL12" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AM12" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="AN12" s="29" t="s">
-        <v>19</v>
-      </c>
-      <c r="AO12" s="32" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="13" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="33"/>
       <c r="B13" s="34">
         <v>1</v>
@@ -1700,7 +1697,7 @@
         <f t="shared" ref="W13:W122" si="0">B13</f>
         <v>1</v>
       </c>
-      <c r="X13" s="62" t="str">
+      <c r="X13" s="54" t="str">
         <f t="shared" ref="X13:X122" si="1">IF(C13="", "",
   IF(AND(D13="", E13=""), "Error: Start position must be specified for Battalion Group",
     IF(OR(D13="", E13=""), "Error: Both X and Y coordinates must be specified",
@@ -1760,7 +1757,7 @@
         "Valid"))))</f>
         <v>Valid</v>
       </c>
-      <c r="AD13" s="53" t="str">
+      <c r="AD13" s="51" t="str">
         <f t="shared" ref="AD13:AD122" si="6">IF(C13="", "",
   IF(AND(J13="", K13=""), "",
     IF(OR(J13="", K13=""), "Error: Both X and Y coordinates must be specified for Destination 1",
@@ -1770,7 +1767,7 @@
         <v>Valid</v>
       </c>
       <c r="AE13" s="52"/>
-      <c r="AF13" s="53" t="str">
+      <c r="AF13" s="51" t="str">
         <f t="shared" ref="AF13:AF122" si="7">IF(C13="", "",
   IF(AND(L13="", M13=""), "",
     IF(OR(L13="", M13=""), "Error: Both X and Y coordinates must be specified for Destination 2",
@@ -1833,7 +1830,7 @@
             "Valid"))))))</f>
         <v/>
       </c>
-      <c r="AL13" s="53" t="str">
+      <c r="AL13" s="51" t="str">
         <f t="shared" ref="AL13:AL122" si="12">IF(C13="", "",
   IF(N13="", "",
     IF(AND(R13="", S13=""), "",
@@ -1844,7 +1841,7 @@
         <v/>
       </c>
       <c r="AM13" s="52"/>
-      <c r="AN13" s="53" t="str">
+      <c r="AN13" s="51" t="str">
         <f t="shared" ref="AN13:AN122" si="13">IF(C13="", "",
   IF(N13="", "",
     IF(AND(T13="", U13=""), "",
@@ -1856,7 +1853,7 @@
       </c>
       <c r="AO13" s="52"/>
     </row>
-    <row r="14" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="33"/>
       <c r="B14" s="34">
         <v>2</v>
@@ -1903,7 +1900,7 @@
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="X14" s="51" t="str">
+      <c r="X14" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -1924,12 +1921,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD14" s="51" t="str">
+      <c r="AD14" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE14" s="52"/>
-      <c r="AF14" s="51" t="str">
+      <c r="AF14" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -1950,18 +1947,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL14" s="51" t="str">
+      <c r="AL14" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM14" s="52"/>
-      <c r="AN14" s="51" t="str">
+      <c r="AN14" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO14" s="52"/>
     </row>
-    <row r="15" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="33"/>
       <c r="B15" s="34">
         <v>3</v>
@@ -2008,7 +2005,7 @@
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="X15" s="53" t="str">
+      <c r="X15" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2029,12 +2026,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD15" s="53" t="str">
+      <c r="AD15" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE15" s="52"/>
-      <c r="AF15" s="53" t="str">
+      <c r="AF15" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2055,18 +2052,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL15" s="53" t="str">
+      <c r="AL15" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM15" s="52"/>
-      <c r="AN15" s="53" t="str">
+      <c r="AN15" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO15" s="52"/>
     </row>
-    <row r="16" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="33"/>
       <c r="B16" s="34">
         <v>4</v>
@@ -2113,7 +2110,7 @@
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="X16" s="51" t="str">
+      <c r="X16" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2134,12 +2131,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD16" s="51" t="str">
+      <c r="AD16" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE16" s="52"/>
-      <c r="AF16" s="51" t="str">
+      <c r="AF16" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2160,18 +2157,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL16" s="51" t="str">
+      <c r="AL16" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM16" s="52"/>
-      <c r="AN16" s="51" t="str">
+      <c r="AN16" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO16" s="52"/>
     </row>
-    <row r="17" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="33"/>
       <c r="B17" s="34">
         <v>5</v>
@@ -2218,7 +2215,7 @@
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="X17" s="53" t="str">
+      <c r="X17" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2239,12 +2236,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD17" s="53" t="str">
+      <c r="AD17" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE17" s="52"/>
-      <c r="AF17" s="53" t="str">
+      <c r="AF17" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2265,18 +2262,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL17" s="53" t="str">
+      <c r="AL17" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM17" s="52"/>
-      <c r="AN17" s="53" t="str">
+      <c r="AN17" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO17" s="52"/>
     </row>
-    <row r="18" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="33"/>
       <c r="B18" s="34">
         <v>6</v>
@@ -2323,7 +2320,7 @@
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="X18" s="51" t="str">
+      <c r="X18" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2344,12 +2341,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD18" s="51" t="str">
+      <c r="AD18" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE18" s="52"/>
-      <c r="AF18" s="51" t="str">
+      <c r="AF18" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2370,18 +2367,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL18" s="51" t="str">
+      <c r="AL18" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM18" s="52"/>
-      <c r="AN18" s="51" t="str">
+      <c r="AN18" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO18" s="52"/>
     </row>
-    <row r="19" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="33"/>
       <c r="B19" s="34">
         <v>7</v>
@@ -2428,7 +2425,7 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="X19" s="53" t="str">
+      <c r="X19" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2449,12 +2446,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD19" s="53" t="str">
+      <c r="AD19" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE19" s="52"/>
-      <c r="AF19" s="53" t="str">
+      <c r="AF19" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2475,18 +2472,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL19" s="53" t="str">
+      <c r="AL19" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM19" s="52"/>
-      <c r="AN19" s="53" t="str">
+      <c r="AN19" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO19" s="52"/>
     </row>
-    <row r="20" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="33"/>
       <c r="B20" s="34">
         <v>8</v>
@@ -2533,7 +2530,7 @@
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="X20" s="51" t="str">
+      <c r="X20" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2554,12 +2551,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD20" s="51" t="str">
+      <c r="AD20" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE20" s="52"/>
-      <c r="AF20" s="51" t="str">
+      <c r="AF20" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2580,18 +2577,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL20" s="51" t="str">
+      <c r="AL20" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM20" s="52"/>
-      <c r="AN20" s="51" t="str">
+      <c r="AN20" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO20" s="52"/>
     </row>
-    <row r="21" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="33"/>
       <c r="B21" s="34">
         <v>9</v>
@@ -2638,7 +2635,7 @@
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="X21" s="53" t="str">
+      <c r="X21" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2659,12 +2656,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD21" s="53" t="str">
+      <c r="AD21" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE21" s="52"/>
-      <c r="AF21" s="53" t="str">
+      <c r="AF21" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2685,18 +2682,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL21" s="53" t="str">
+      <c r="AL21" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM21" s="52"/>
-      <c r="AN21" s="53" t="str">
+      <c r="AN21" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO21" s="52"/>
     </row>
-    <row r="22" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="33"/>
       <c r="B22" s="34">
         <v>10</v>
@@ -2743,7 +2740,7 @@
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
-      <c r="X22" s="51" t="str">
+      <c r="X22" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2764,12 +2761,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD22" s="51" t="str">
+      <c r="AD22" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE22" s="52"/>
-      <c r="AF22" s="51" t="str">
+      <c r="AF22" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2790,18 +2787,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL22" s="51" t="str">
+      <c r="AL22" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM22" s="52"/>
-      <c r="AN22" s="51" t="str">
+      <c r="AN22" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO22" s="52"/>
     </row>
-    <row r="23" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="33"/>
       <c r="B23" s="34">
         <v>11</v>
@@ -2848,7 +2845,7 @@
         <f t="shared" si="0"/>
         <v>11</v>
       </c>
-      <c r="X23" s="53" t="str">
+      <c r="X23" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2869,12 +2866,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD23" s="53" t="str">
+      <c r="AD23" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE23" s="52"/>
-      <c r="AF23" s="53" t="str">
+      <c r="AF23" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -2895,18 +2892,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL23" s="53" t="str">
+      <c r="AL23" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM23" s="52"/>
-      <c r="AN23" s="53" t="str">
+      <c r="AN23" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO23" s="52"/>
     </row>
-    <row r="24" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="33"/>
       <c r="B24" s="34">
         <v>12</v>
@@ -2953,7 +2950,7 @@
         <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="X24" s="51" t="str">
+      <c r="X24" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -2974,12 +2971,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD24" s="51" t="str">
+      <c r="AD24" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE24" s="52"/>
-      <c r="AF24" s="51" t="str">
+      <c r="AF24" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3000,18 +2997,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL24" s="51" t="str">
+      <c r="AL24" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM24" s="52"/>
-      <c r="AN24" s="51" t="str">
+      <c r="AN24" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO24" s="52"/>
     </row>
-    <row r="25" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="33"/>
       <c r="B25" s="34">
         <v>13</v>
@@ -3058,7 +3055,7 @@
         <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="X25" s="53" t="str">
+      <c r="X25" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3079,12 +3076,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD25" s="53" t="str">
+      <c r="AD25" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE25" s="52"/>
-      <c r="AF25" s="53" t="str">
+      <c r="AF25" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3105,18 +3102,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL25" s="53" t="str">
+      <c r="AL25" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM25" s="52"/>
-      <c r="AN25" s="53" t="str">
+      <c r="AN25" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO25" s="52"/>
     </row>
-    <row r="26" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="33"/>
       <c r="B26" s="34">
         <v>14</v>
@@ -3163,7 +3160,7 @@
         <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="X26" s="51" t="str">
+      <c r="X26" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3184,12 +3181,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD26" s="51" t="str">
+      <c r="AD26" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE26" s="52"/>
-      <c r="AF26" s="51" t="str">
+      <c r="AF26" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3210,18 +3207,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL26" s="51" t="str">
+      <c r="AL26" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM26" s="52"/>
-      <c r="AN26" s="51" t="str">
+      <c r="AN26" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO26" s="52"/>
     </row>
-    <row r="27" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="33"/>
       <c r="B27" s="34">
         <v>15</v>
@@ -3268,7 +3265,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="X27" s="53" t="str">
+      <c r="X27" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3289,12 +3286,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD27" s="53" t="str">
+      <c r="AD27" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE27" s="52"/>
-      <c r="AF27" s="53" t="str">
+      <c r="AF27" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3315,18 +3312,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL27" s="53" t="str">
+      <c r="AL27" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM27" s="52"/>
-      <c r="AN27" s="53" t="str">
+      <c r="AN27" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO27" s="52"/>
     </row>
-    <row r="28" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="33"/>
       <c r="B28" s="34">
         <v>16</v>
@@ -3373,7 +3370,7 @@
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="X28" s="51" t="str">
+      <c r="X28" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3394,12 +3391,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD28" s="51" t="str">
+      <c r="AD28" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE28" s="52"/>
-      <c r="AF28" s="51" t="str">
+      <c r="AF28" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3420,18 +3417,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL28" s="51" t="str">
+      <c r="AL28" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM28" s="52"/>
-      <c r="AN28" s="51" t="str">
+      <c r="AN28" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO28" s="52"/>
     </row>
-    <row r="29" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="33"/>
       <c r="B29" s="34">
         <v>17</v>
@@ -3478,7 +3475,7 @@
         <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="X29" s="53" t="str">
+      <c r="X29" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3499,12 +3496,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD29" s="53" t="str">
+      <c r="AD29" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE29" s="52"/>
-      <c r="AF29" s="53" t="str">
+      <c r="AF29" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3525,18 +3522,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL29" s="53" t="str">
+      <c r="AL29" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM29" s="52"/>
-      <c r="AN29" s="53" t="str">
+      <c r="AN29" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO29" s="52"/>
     </row>
-    <row r="30" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="33"/>
       <c r="B30" s="34">
         <v>18</v>
@@ -3583,7 +3580,7 @@
         <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="X30" s="51" t="str">
+      <c r="X30" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3604,12 +3601,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD30" s="51" t="str">
+      <c r="AD30" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE30" s="52"/>
-      <c r="AF30" s="51" t="str">
+      <c r="AF30" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3630,18 +3627,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL30" s="51" t="str">
+      <c r="AL30" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM30" s="52"/>
-      <c r="AN30" s="51" t="str">
+      <c r="AN30" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO30" s="52"/>
     </row>
-    <row r="31" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="33"/>
       <c r="B31" s="34">
         <v>19</v>
@@ -3688,7 +3685,7 @@
         <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="X31" s="53" t="str">
+      <c r="X31" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3709,12 +3706,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD31" s="53" t="str">
+      <c r="AD31" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE31" s="52"/>
-      <c r="AF31" s="53" t="str">
+      <c r="AF31" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3735,18 +3732,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL31" s="53" t="str">
+      <c r="AL31" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM31" s="52"/>
-      <c r="AN31" s="53" t="str">
+      <c r="AN31" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO31" s="52"/>
     </row>
-    <row r="32" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="33"/>
       <c r="B32" s="34">
         <v>20</v>
@@ -3793,7 +3790,7 @@
         <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="X32" s="51" t="str">
+      <c r="X32" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3814,12 +3811,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD32" s="51" t="str">
+      <c r="AD32" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE32" s="52"/>
-      <c r="AF32" s="51" t="str">
+      <c r="AF32" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3840,18 +3837,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL32" s="51" t="str">
+      <c r="AL32" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM32" s="52"/>
-      <c r="AN32" s="51" t="str">
+      <c r="AN32" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO32" s="52"/>
     </row>
-    <row r="33" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="33"/>
       <c r="B33" s="34">
         <v>21</v>
@@ -3898,7 +3895,7 @@
         <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="X33" s="53" t="str">
+      <c r="X33" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -3919,12 +3916,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD33" s="53" t="str">
+      <c r="AD33" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE33" s="52"/>
-      <c r="AF33" s="53" t="str">
+      <c r="AF33" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -3945,18 +3942,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL33" s="53" t="str">
+      <c r="AL33" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM33" s="52"/>
-      <c r="AN33" s="53" t="str">
+      <c r="AN33" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO33" s="52"/>
     </row>
-    <row r="34" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="33"/>
       <c r="B34" s="34">
         <v>22</v>
@@ -4003,7 +4000,7 @@
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="X34" s="51" t="str">
+      <c r="X34" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4024,12 +4021,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD34" s="51" t="str">
+      <c r="AD34" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE34" s="52"/>
-      <c r="AF34" s="51" t="str">
+      <c r="AF34" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4050,18 +4047,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL34" s="51" t="str">
+      <c r="AL34" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM34" s="52"/>
-      <c r="AN34" s="51" t="str">
+      <c r="AN34" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO34" s="52"/>
     </row>
-    <row r="35" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="33"/>
       <c r="B35" s="34">
         <v>23</v>
@@ -4108,7 +4105,7 @@
         <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="X35" s="53" t="str">
+      <c r="X35" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4129,12 +4126,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD35" s="53" t="str">
+      <c r="AD35" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE35" s="52"/>
-      <c r="AF35" s="53" t="str">
+      <c r="AF35" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4155,18 +4152,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL35" s="53" t="str">
+      <c r="AL35" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM35" s="52"/>
-      <c r="AN35" s="53" t="str">
+      <c r="AN35" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO35" s="52"/>
     </row>
-    <row r="36" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="33"/>
       <c r="B36" s="34">
         <v>24</v>
@@ -4213,7 +4210,7 @@
         <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="X36" s="51" t="str">
+      <c r="X36" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4234,12 +4231,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD36" s="51" t="str">
+      <c r="AD36" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE36" s="52"/>
-      <c r="AF36" s="51" t="str">
+      <c r="AF36" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4260,18 +4257,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL36" s="51" t="str">
+      <c r="AL36" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM36" s="52"/>
-      <c r="AN36" s="51" t="str">
+      <c r="AN36" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO36" s="52"/>
     </row>
-    <row r="37" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="33"/>
       <c r="B37" s="34">
         <v>25</v>
@@ -4318,7 +4315,7 @@
         <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="X37" s="53" t="str">
+      <c r="X37" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4339,12 +4336,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD37" s="53" t="str">
+      <c r="AD37" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE37" s="52"/>
-      <c r="AF37" s="53" t="str">
+      <c r="AF37" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4365,18 +4362,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL37" s="53" t="str">
+      <c r="AL37" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM37" s="52"/>
-      <c r="AN37" s="53" t="str">
+      <c r="AN37" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO37" s="52"/>
     </row>
-    <row r="38" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="33"/>
       <c r="B38" s="34">
         <v>26</v>
@@ -4423,7 +4420,7 @@
         <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="X38" s="51" t="str">
+      <c r="X38" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4444,12 +4441,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD38" s="51" t="str">
+      <c r="AD38" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE38" s="52"/>
-      <c r="AF38" s="51" t="str">
+      <c r="AF38" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4470,18 +4467,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL38" s="51" t="str">
+      <c r="AL38" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM38" s="52"/>
-      <c r="AN38" s="51" t="str">
+      <c r="AN38" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO38" s="52"/>
     </row>
-    <row r="39" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="33"/>
       <c r="B39" s="34">
         <v>27</v>
@@ -4528,7 +4525,7 @@
         <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="X39" s="53" t="str">
+      <c r="X39" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4549,12 +4546,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD39" s="53" t="str">
+      <c r="AD39" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE39" s="52"/>
-      <c r="AF39" s="53" t="str">
+      <c r="AF39" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4575,18 +4572,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL39" s="53" t="str">
+      <c r="AL39" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM39" s="52"/>
-      <c r="AN39" s="53" t="str">
+      <c r="AN39" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO39" s="52"/>
     </row>
-    <row r="40" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="33"/>
       <c r="B40" s="34">
         <v>28</v>
@@ -4633,7 +4630,7 @@
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="X40" s="51" t="str">
+      <c r="X40" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4654,12 +4651,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD40" s="51" t="str">
+      <c r="AD40" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE40" s="52"/>
-      <c r="AF40" s="51" t="str">
+      <c r="AF40" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4680,18 +4677,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL40" s="51" t="str">
+      <c r="AL40" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM40" s="52"/>
-      <c r="AN40" s="51" t="str">
+      <c r="AN40" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO40" s="52"/>
     </row>
-    <row r="41" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="33"/>
       <c r="B41" s="34">
         <v>29</v>
@@ -4738,7 +4735,7 @@
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="X41" s="53" t="str">
+      <c r="X41" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4759,12 +4756,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD41" s="53" t="str">
+      <c r="AD41" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE41" s="52"/>
-      <c r="AF41" s="53" t="str">
+      <c r="AF41" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4785,18 +4782,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL41" s="53" t="str">
+      <c r="AL41" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM41" s="52"/>
-      <c r="AN41" s="53" t="str">
+      <c r="AN41" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO41" s="52"/>
     </row>
-    <row r="42" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="33"/>
       <c r="B42" s="34">
         <v>30</v>
@@ -4843,7 +4840,7 @@
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="X42" s="51" t="str">
+      <c r="X42" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4864,12 +4861,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD42" s="51" t="str">
+      <c r="AD42" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE42" s="52"/>
-      <c r="AF42" s="51" t="str">
+      <c r="AF42" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4890,18 +4887,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL42" s="51" t="str">
+      <c r="AL42" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM42" s="52"/>
-      <c r="AN42" s="51" t="str">
+      <c r="AN42" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO42" s="52"/>
     </row>
-    <row r="43" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="33"/>
       <c r="B43" s="34">
         <v>31</v>
@@ -4948,7 +4945,7 @@
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="X43" s="53" t="str">
+      <c r="X43" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -4969,12 +4966,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD43" s="53" t="str">
+      <c r="AD43" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE43" s="52"/>
-      <c r="AF43" s="53" t="str">
+      <c r="AF43" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -4995,18 +4992,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL43" s="53" t="str">
+      <c r="AL43" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM43" s="52"/>
-      <c r="AN43" s="53" t="str">
+      <c r="AN43" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO43" s="52"/>
     </row>
-    <row r="44" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="33"/>
       <c r="B44" s="34">
         <v>32</v>
@@ -5053,7 +5050,7 @@
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="X44" s="51" t="str">
+      <c r="X44" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5074,12 +5071,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD44" s="51" t="str">
+      <c r="AD44" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE44" s="52"/>
-      <c r="AF44" s="51" t="str">
+      <c r="AF44" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5100,18 +5097,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL44" s="51" t="str">
+      <c r="AL44" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM44" s="52"/>
-      <c r="AN44" s="51" t="str">
+      <c r="AN44" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO44" s="52"/>
     </row>
-    <row r="45" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="33"/>
       <c r="B45" s="34">
         <v>33</v>
@@ -5158,7 +5155,7 @@
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="X45" s="53" t="str">
+      <c r="X45" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5179,12 +5176,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD45" s="53" t="str">
+      <c r="AD45" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE45" s="52"/>
-      <c r="AF45" s="53" t="str">
+      <c r="AF45" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5205,18 +5202,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL45" s="53" t="str">
+      <c r="AL45" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM45" s="52"/>
-      <c r="AN45" s="53" t="str">
+      <c r="AN45" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO45" s="52"/>
     </row>
-    <row r="46" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="33"/>
       <c r="B46" s="34">
         <v>34</v>
@@ -5263,7 +5260,7 @@
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="X46" s="51" t="str">
+      <c r="X46" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5284,12 +5281,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD46" s="51" t="str">
+      <c r="AD46" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE46" s="52"/>
-      <c r="AF46" s="51" t="str">
+      <c r="AF46" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5310,18 +5307,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL46" s="51" t="str">
+      <c r="AL46" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM46" s="52"/>
-      <c r="AN46" s="51" t="str">
+      <c r="AN46" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO46" s="52"/>
     </row>
-    <row r="47" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="33"/>
       <c r="B47" s="34">
         <v>35</v>
@@ -5368,7 +5365,7 @@
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="X47" s="53" t="str">
+      <c r="X47" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5389,12 +5386,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD47" s="53" t="str">
+      <c r="AD47" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE47" s="52"/>
-      <c r="AF47" s="53" t="str">
+      <c r="AF47" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5415,18 +5412,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL47" s="53" t="str">
+      <c r="AL47" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM47" s="52"/>
-      <c r="AN47" s="53" t="str">
+      <c r="AN47" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO47" s="52"/>
     </row>
-    <row r="48" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="33"/>
       <c r="B48" s="34">
         <v>36</v>
@@ -5473,7 +5470,7 @@
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="X48" s="51" t="str">
+      <c r="X48" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5494,12 +5491,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD48" s="51" t="str">
+      <c r="AD48" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE48" s="52"/>
-      <c r="AF48" s="51" t="str">
+      <c r="AF48" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5520,18 +5517,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL48" s="51" t="str">
+      <c r="AL48" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM48" s="52"/>
-      <c r="AN48" s="51" t="str">
+      <c r="AN48" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO48" s="52"/>
     </row>
-    <row r="49" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="33"/>
       <c r="B49" s="34">
         <v>37</v>
@@ -5578,7 +5575,7 @@
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="X49" s="53" t="str">
+      <c r="X49" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5599,12 +5596,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD49" s="53" t="str">
+      <c r="AD49" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE49" s="52"/>
-      <c r="AF49" s="53" t="str">
+      <c r="AF49" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5625,18 +5622,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL49" s="53" t="str">
+      <c r="AL49" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM49" s="52"/>
-      <c r="AN49" s="53" t="str">
+      <c r="AN49" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO49" s="52"/>
     </row>
-    <row r="50" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="33"/>
       <c r="B50" s="34">
         <v>38</v>
@@ -5683,7 +5680,7 @@
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="X50" s="51" t="str">
+      <c r="X50" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5704,12 +5701,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD50" s="51" t="str">
+      <c r="AD50" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE50" s="52"/>
-      <c r="AF50" s="51" t="str">
+      <c r="AF50" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5730,18 +5727,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL50" s="51" t="str">
+      <c r="AL50" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM50" s="52"/>
-      <c r="AN50" s="51" t="str">
+      <c r="AN50" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO50" s="52"/>
     </row>
-    <row r="51" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="33"/>
       <c r="B51" s="34">
         <v>39</v>
@@ -5788,7 +5785,7 @@
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="X51" s="53" t="str">
+      <c r="X51" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5809,12 +5806,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD51" s="53" t="str">
+      <c r="AD51" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE51" s="52"/>
-      <c r="AF51" s="53" t="str">
+      <c r="AF51" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5835,18 +5832,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL51" s="53" t="str">
+      <c r="AL51" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM51" s="52"/>
-      <c r="AN51" s="53" t="str">
+      <c r="AN51" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO51" s="52"/>
     </row>
-    <row r="52" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="33"/>
       <c r="B52" s="34">
         <v>40</v>
@@ -5893,7 +5890,7 @@
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="X52" s="51" t="str">
+      <c r="X52" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -5914,12 +5911,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD52" s="51" t="str">
+      <c r="AD52" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE52" s="52"/>
-      <c r="AF52" s="51" t="str">
+      <c r="AF52" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -5940,18 +5937,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL52" s="51" t="str">
+      <c r="AL52" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM52" s="52"/>
-      <c r="AN52" s="51" t="str">
+      <c r="AN52" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO52" s="52"/>
     </row>
-    <row r="53" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="33"/>
       <c r="B53" s="34">
         <v>41</v>
@@ -5998,7 +5995,7 @@
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="X53" s="53" t="str">
+      <c r="X53" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6019,12 +6016,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD53" s="53" t="str">
+      <c r="AD53" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE53" s="52"/>
-      <c r="AF53" s="53" t="str">
+      <c r="AF53" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6045,18 +6042,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL53" s="53" t="str">
+      <c r="AL53" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM53" s="52"/>
-      <c r="AN53" s="53" t="str">
+      <c r="AN53" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO53" s="52"/>
     </row>
-    <row r="54" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="33"/>
       <c r="B54" s="34">
         <v>42</v>
@@ -6103,7 +6100,7 @@
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="X54" s="51" t="str">
+      <c r="X54" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6124,12 +6121,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD54" s="51" t="str">
+      <c r="AD54" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE54" s="52"/>
-      <c r="AF54" s="51" t="str">
+      <c r="AF54" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6150,18 +6147,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL54" s="51" t="str">
+      <c r="AL54" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM54" s="52"/>
-      <c r="AN54" s="51" t="str">
+      <c r="AN54" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO54" s="52"/>
     </row>
-    <row r="55" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="33"/>
       <c r="B55" s="34">
         <v>43</v>
@@ -6208,7 +6205,7 @@
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="X55" s="53" t="str">
+      <c r="X55" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6229,12 +6226,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD55" s="53" t="str">
+      <c r="AD55" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE55" s="52"/>
-      <c r="AF55" s="53" t="str">
+      <c r="AF55" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6255,18 +6252,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL55" s="53" t="str">
+      <c r="AL55" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM55" s="52"/>
-      <c r="AN55" s="53" t="str">
+      <c r="AN55" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO55" s="52"/>
     </row>
-    <row r="56" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="33"/>
       <c r="B56" s="34">
         <v>44</v>
@@ -6313,7 +6310,7 @@
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="X56" s="51" t="str">
+      <c r="X56" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6334,12 +6331,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD56" s="51" t="str">
+      <c r="AD56" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE56" s="52"/>
-      <c r="AF56" s="51" t="str">
+      <c r="AF56" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6360,18 +6357,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL56" s="51" t="str">
+      <c r="AL56" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM56" s="52"/>
-      <c r="AN56" s="51" t="str">
+      <c r="AN56" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO56" s="52"/>
     </row>
-    <row r="57" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="33"/>
       <c r="B57" s="34">
         <v>45</v>
@@ -6418,7 +6415,7 @@
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="X57" s="53" t="str">
+      <c r="X57" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6439,12 +6436,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD57" s="53" t="str">
+      <c r="AD57" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE57" s="52"/>
-      <c r="AF57" s="53" t="str">
+      <c r="AF57" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6465,18 +6462,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL57" s="53" t="str">
+      <c r="AL57" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM57" s="52"/>
-      <c r="AN57" s="53" t="str">
+      <c r="AN57" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO57" s="52"/>
     </row>
-    <row r="58" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="33"/>
       <c r="B58" s="34">
         <v>46</v>
@@ -6523,7 +6520,7 @@
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="X58" s="51" t="str">
+      <c r="X58" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6544,12 +6541,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD58" s="51" t="str">
+      <c r="AD58" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE58" s="52"/>
-      <c r="AF58" s="51" t="str">
+      <c r="AF58" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6570,18 +6567,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL58" s="51" t="str">
+      <c r="AL58" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM58" s="52"/>
-      <c r="AN58" s="51" t="str">
+      <c r="AN58" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO58" s="52"/>
     </row>
-    <row r="59" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="33"/>
       <c r="B59" s="34">
         <v>47</v>
@@ -6628,7 +6625,7 @@
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="X59" s="53" t="str">
+      <c r="X59" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6649,12 +6646,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD59" s="53" t="str">
+      <c r="AD59" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE59" s="52"/>
-      <c r="AF59" s="53" t="str">
+      <c r="AF59" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6675,18 +6672,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL59" s="53" t="str">
+      <c r="AL59" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM59" s="52"/>
-      <c r="AN59" s="53" t="str">
+      <c r="AN59" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO59" s="52"/>
     </row>
-    <row r="60" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="33"/>
       <c r="B60" s="34">
         <v>48</v>
@@ -6733,7 +6730,7 @@
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="X60" s="51" t="str">
+      <c r="X60" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6754,12 +6751,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD60" s="51" t="str">
+      <c r="AD60" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE60" s="52"/>
-      <c r="AF60" s="51" t="str">
+      <c r="AF60" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6780,18 +6777,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL60" s="51" t="str">
+      <c r="AL60" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM60" s="52"/>
-      <c r="AN60" s="51" t="str">
+      <c r="AN60" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO60" s="52"/>
     </row>
-    <row r="61" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="33"/>
       <c r="B61" s="34">
         <v>49</v>
@@ -6838,7 +6835,7 @@
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="X61" s="53" t="str">
+      <c r="X61" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6859,12 +6856,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD61" s="53" t="str">
+      <c r="AD61" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE61" s="52"/>
-      <c r="AF61" s="53" t="str">
+      <c r="AF61" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6885,18 +6882,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL61" s="53" t="str">
+      <c r="AL61" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM61" s="52"/>
-      <c r="AN61" s="53" t="str">
+      <c r="AN61" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO61" s="52"/>
     </row>
-    <row r="62" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="33"/>
       <c r="B62" s="34">
         <v>50</v>
@@ -6943,7 +6940,7 @@
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="X62" s="51" t="str">
+      <c r="X62" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -6964,12 +6961,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD62" s="51" t="str">
+      <c r="AD62" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE62" s="52"/>
-      <c r="AF62" s="51" t="str">
+      <c r="AF62" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -6990,18 +6987,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL62" s="51" t="str">
+      <c r="AL62" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM62" s="52"/>
-      <c r="AN62" s="51" t="str">
+      <c r="AN62" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO62" s="52"/>
     </row>
-    <row r="63" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="33"/>
       <c r="B63" s="34">
         <v>51</v>
@@ -7048,7 +7045,7 @@
         <f t="shared" si="0"/>
         <v>51</v>
       </c>
-      <c r="X63" s="53" t="str">
+      <c r="X63" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7069,12 +7066,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD63" s="53" t="str">
+      <c r="AD63" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE63" s="52"/>
-      <c r="AF63" s="53" t="str">
+      <c r="AF63" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7095,18 +7092,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL63" s="53" t="str">
+      <c r="AL63" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM63" s="52"/>
-      <c r="AN63" s="53" t="str">
+      <c r="AN63" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO63" s="52"/>
     </row>
-    <row r="64" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="33"/>
       <c r="B64" s="34">
         <v>52</v>
@@ -7153,7 +7150,7 @@
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-      <c r="X64" s="51" t="str">
+      <c r="X64" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7174,12 +7171,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD64" s="51" t="str">
+      <c r="AD64" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE64" s="52"/>
-      <c r="AF64" s="51" t="str">
+      <c r="AF64" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7200,18 +7197,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL64" s="51" t="str">
+      <c r="AL64" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM64" s="52"/>
-      <c r="AN64" s="51" t="str">
+      <c r="AN64" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO64" s="52"/>
     </row>
-    <row r="65" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="33"/>
       <c r="B65" s="34">
         <v>53</v>
@@ -7258,7 +7255,7 @@
         <f t="shared" si="0"/>
         <v>53</v>
       </c>
-      <c r="X65" s="53" t="str">
+      <c r="X65" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7279,12 +7276,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD65" s="53" t="str">
+      <c r="AD65" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE65" s="52"/>
-      <c r="AF65" s="53" t="str">
+      <c r="AF65" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7305,18 +7302,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL65" s="53" t="str">
+      <c r="AL65" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM65" s="52"/>
-      <c r="AN65" s="53" t="str">
+      <c r="AN65" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO65" s="52"/>
     </row>
-    <row r="66" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="33"/>
       <c r="B66" s="34">
         <v>54</v>
@@ -7363,7 +7360,7 @@
         <f t="shared" si="0"/>
         <v>54</v>
       </c>
-      <c r="X66" s="51" t="str">
+      <c r="X66" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7384,12 +7381,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD66" s="51" t="str">
+      <c r="AD66" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE66" s="52"/>
-      <c r="AF66" s="51" t="str">
+      <c r="AF66" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7410,18 +7407,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL66" s="51" t="str">
+      <c r="AL66" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM66" s="52"/>
-      <c r="AN66" s="51" t="str">
+      <c r="AN66" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO66" s="52"/>
     </row>
-    <row r="67" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="33"/>
       <c r="B67" s="34">
         <v>55</v>
@@ -7468,7 +7465,7 @@
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-      <c r="X67" s="53" t="str">
+      <c r="X67" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7489,12 +7486,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD67" s="53" t="str">
+      <c r="AD67" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE67" s="52"/>
-      <c r="AF67" s="53" t="str">
+      <c r="AF67" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7515,18 +7512,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL67" s="53" t="str">
+      <c r="AL67" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM67" s="52"/>
-      <c r="AN67" s="53" t="str">
+      <c r="AN67" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO67" s="52"/>
     </row>
-    <row r="68" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="33"/>
       <c r="B68" s="34">
         <v>56</v>
@@ -7573,7 +7570,7 @@
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-      <c r="X68" s="51" t="str">
+      <c r="X68" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7594,12 +7591,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD68" s="51" t="str">
+      <c r="AD68" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE68" s="52"/>
-      <c r="AF68" s="51" t="str">
+      <c r="AF68" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7620,18 +7617,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL68" s="51" t="str">
+      <c r="AL68" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM68" s="52"/>
-      <c r="AN68" s="51" t="str">
+      <c r="AN68" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO68" s="52"/>
     </row>
-    <row r="69" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="33"/>
       <c r="B69" s="34">
         <v>57</v>
@@ -7678,7 +7675,7 @@
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-      <c r="X69" s="53" t="str">
+      <c r="X69" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7699,12 +7696,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD69" s="53" t="str">
+      <c r="AD69" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE69" s="52"/>
-      <c r="AF69" s="53" t="str">
+      <c r="AF69" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7725,18 +7722,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL69" s="53" t="str">
+      <c r="AL69" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM69" s="52"/>
-      <c r="AN69" s="53" t="str">
+      <c r="AN69" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO69" s="52"/>
     </row>
-    <row r="70" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="33"/>
       <c r="B70" s="34">
         <v>58</v>
@@ -7783,7 +7780,7 @@
         <f t="shared" si="0"/>
         <v>58</v>
       </c>
-      <c r="X70" s="51" t="str">
+      <c r="X70" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7804,12 +7801,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD70" s="51" t="str">
+      <c r="AD70" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE70" s="52"/>
-      <c r="AF70" s="51" t="str">
+      <c r="AF70" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7830,18 +7827,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL70" s="51" t="str">
+      <c r="AL70" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM70" s="52"/>
-      <c r="AN70" s="51" t="str">
+      <c r="AN70" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO70" s="52"/>
     </row>
-    <row r="71" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="33"/>
       <c r="B71" s="34">
         <v>59</v>
@@ -7888,7 +7885,7 @@
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-      <c r="X71" s="53" t="str">
+      <c r="X71" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -7909,12 +7906,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD71" s="53" t="str">
+      <c r="AD71" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE71" s="52"/>
-      <c r="AF71" s="53" t="str">
+      <c r="AF71" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -7935,18 +7932,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL71" s="53" t="str">
+      <c r="AL71" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM71" s="52"/>
-      <c r="AN71" s="53" t="str">
+      <c r="AN71" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO71" s="52"/>
     </row>
-    <row r="72" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="33"/>
       <c r="B72" s="34">
         <v>60</v>
@@ -7993,7 +7990,7 @@
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="X72" s="51" t="str">
+      <c r="X72" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8014,12 +8011,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD72" s="51" t="str">
+      <c r="AD72" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE72" s="52"/>
-      <c r="AF72" s="51" t="str">
+      <c r="AF72" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8040,18 +8037,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL72" s="51" t="str">
+      <c r="AL72" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM72" s="52"/>
-      <c r="AN72" s="51" t="str">
+      <c r="AN72" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO72" s="52"/>
     </row>
-    <row r="73" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="33"/>
       <c r="B73" s="34">
         <v>61</v>
@@ -8098,7 +8095,7 @@
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-      <c r="X73" s="53" t="str">
+      <c r="X73" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8119,12 +8116,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD73" s="53" t="str">
+      <c r="AD73" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE73" s="52"/>
-      <c r="AF73" s="53" t="str">
+      <c r="AF73" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8145,18 +8142,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL73" s="53" t="str">
+      <c r="AL73" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM73" s="52"/>
-      <c r="AN73" s="53" t="str">
+      <c r="AN73" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO73" s="52"/>
     </row>
-    <row r="74" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="33"/>
       <c r="B74" s="34">
         <v>62</v>
@@ -8203,7 +8200,7 @@
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-      <c r="X74" s="51" t="str">
+      <c r="X74" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8224,12 +8221,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD74" s="51" t="str">
+      <c r="AD74" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE74" s="52"/>
-      <c r="AF74" s="51" t="str">
+      <c r="AF74" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8250,18 +8247,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL74" s="51" t="str">
+      <c r="AL74" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM74" s="52"/>
-      <c r="AN74" s="51" t="str">
+      <c r="AN74" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO74" s="52"/>
     </row>
-    <row r="75" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="33"/>
       <c r="B75" s="34">
         <v>63</v>
@@ -8308,7 +8305,7 @@
         <f t="shared" si="0"/>
         <v>63</v>
       </c>
-      <c r="X75" s="53" t="str">
+      <c r="X75" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8329,12 +8326,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD75" s="53" t="str">
+      <c r="AD75" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE75" s="52"/>
-      <c r="AF75" s="53" t="str">
+      <c r="AF75" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8355,18 +8352,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL75" s="53" t="str">
+      <c r="AL75" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM75" s="52"/>
-      <c r="AN75" s="53" t="str">
+      <c r="AN75" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO75" s="52"/>
     </row>
-    <row r="76" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="33"/>
       <c r="B76" s="34">
         <v>64</v>
@@ -8413,7 +8410,7 @@
         <f t="shared" si="0"/>
         <v>64</v>
       </c>
-      <c r="X76" s="51" t="str">
+      <c r="X76" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8434,12 +8431,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD76" s="51" t="str">
+      <c r="AD76" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE76" s="52"/>
-      <c r="AF76" s="51" t="str">
+      <c r="AF76" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8460,18 +8457,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL76" s="51" t="str">
+      <c r="AL76" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM76" s="52"/>
-      <c r="AN76" s="51" t="str">
+      <c r="AN76" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO76" s="52"/>
     </row>
-    <row r="77" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="33"/>
       <c r="B77" s="34">
         <v>65</v>
@@ -8518,7 +8515,7 @@
         <f t="shared" si="0"/>
         <v>65</v>
       </c>
-      <c r="X77" s="53" t="str">
+      <c r="X77" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8539,12 +8536,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD77" s="53" t="str">
+      <c r="AD77" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE77" s="52"/>
-      <c r="AF77" s="53" t="str">
+      <c r="AF77" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8565,18 +8562,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL77" s="53" t="str">
+      <c r="AL77" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM77" s="52"/>
-      <c r="AN77" s="53" t="str">
+      <c r="AN77" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO77" s="52"/>
     </row>
-    <row r="78" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="33"/>
       <c r="B78" s="34">
         <v>66</v>
@@ -8623,7 +8620,7 @@
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-      <c r="X78" s="51" t="str">
+      <c r="X78" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8644,12 +8641,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD78" s="51" t="str">
+      <c r="AD78" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE78" s="52"/>
-      <c r="AF78" s="51" t="str">
+      <c r="AF78" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8670,18 +8667,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL78" s="51" t="str">
+      <c r="AL78" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM78" s="52"/>
-      <c r="AN78" s="51" t="str">
+      <c r="AN78" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO78" s="52"/>
     </row>
-    <row r="79" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="33"/>
       <c r="B79" s="34">
         <v>67</v>
@@ -8728,7 +8725,7 @@
         <f t="shared" si="0"/>
         <v>67</v>
       </c>
-      <c r="X79" s="53" t="str">
+      <c r="X79" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8749,12 +8746,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD79" s="53" t="str">
+      <c r="AD79" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE79" s="52"/>
-      <c r="AF79" s="53" t="str">
+      <c r="AF79" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8775,18 +8772,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL79" s="53" t="str">
+      <c r="AL79" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM79" s="52"/>
-      <c r="AN79" s="53" t="str">
+      <c r="AN79" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO79" s="52"/>
     </row>
-    <row r="80" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="33"/>
       <c r="B80" s="34">
         <v>68</v>
@@ -8833,7 +8830,7 @@
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-      <c r="X80" s="51" t="str">
+      <c r="X80" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8854,12 +8851,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD80" s="51" t="str">
+      <c r="AD80" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE80" s="52"/>
-      <c r="AF80" s="51" t="str">
+      <c r="AF80" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8880,18 +8877,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL80" s="51" t="str">
+      <c r="AL80" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM80" s="52"/>
-      <c r="AN80" s="51" t="str">
+      <c r="AN80" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO80" s="52"/>
     </row>
-    <row r="81" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="33"/>
       <c r="B81" s="34">
         <v>69</v>
@@ -8938,7 +8935,7 @@
         <f t="shared" si="0"/>
         <v>69</v>
       </c>
-      <c r="X81" s="53" t="str">
+      <c r="X81" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -8959,12 +8956,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD81" s="53" t="str">
+      <c r="AD81" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE81" s="52"/>
-      <c r="AF81" s="53" t="str">
+      <c r="AF81" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -8985,18 +8982,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL81" s="53" t="str">
+      <c r="AL81" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM81" s="52"/>
-      <c r="AN81" s="53" t="str">
+      <c r="AN81" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO81" s="52"/>
     </row>
-    <row r="82" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="33"/>
       <c r="B82" s="34">
         <v>70</v>
@@ -9043,7 +9040,7 @@
         <f t="shared" si="0"/>
         <v>70</v>
       </c>
-      <c r="X82" s="51" t="str">
+      <c r="X82" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9064,12 +9061,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD82" s="51" t="str">
+      <c r="AD82" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE82" s="52"/>
-      <c r="AF82" s="51" t="str">
+      <c r="AF82" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9090,18 +9087,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL82" s="51" t="str">
+      <c r="AL82" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM82" s="52"/>
-      <c r="AN82" s="51" t="str">
+      <c r="AN82" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO82" s="52"/>
     </row>
-    <row r="83" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="33"/>
       <c r="B83" s="34">
         <v>71</v>
@@ -9148,7 +9145,7 @@
         <f t="shared" si="0"/>
         <v>71</v>
       </c>
-      <c r="X83" s="53" t="str">
+      <c r="X83" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9169,12 +9166,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD83" s="53" t="str">
+      <c r="AD83" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE83" s="52"/>
-      <c r="AF83" s="53" t="str">
+      <c r="AF83" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9195,18 +9192,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL83" s="53" t="str">
+      <c r="AL83" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM83" s="52"/>
-      <c r="AN83" s="53" t="str">
+      <c r="AN83" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO83" s="52"/>
     </row>
-    <row r="84" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="33"/>
       <c r="B84" s="34">
         <v>72</v>
@@ -9253,7 +9250,7 @@
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-      <c r="X84" s="51" t="str">
+      <c r="X84" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9274,12 +9271,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD84" s="51" t="str">
+      <c r="AD84" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE84" s="52"/>
-      <c r="AF84" s="51" t="str">
+      <c r="AF84" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9300,18 +9297,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL84" s="51" t="str">
+      <c r="AL84" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM84" s="52"/>
-      <c r="AN84" s="51" t="str">
+      <c r="AN84" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO84" s="52"/>
     </row>
-    <row r="85" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="33"/>
       <c r="B85" s="34">
         <v>73</v>
@@ -9358,7 +9355,7 @@
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="X85" s="53" t="str">
+      <c r="X85" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9379,12 +9376,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD85" s="53" t="str">
+      <c r="AD85" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE85" s="52"/>
-      <c r="AF85" s="53" t="str">
+      <c r="AF85" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9405,18 +9402,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL85" s="53" t="str">
+      <c r="AL85" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM85" s="52"/>
-      <c r="AN85" s="53" t="str">
+      <c r="AN85" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO85" s="52"/>
     </row>
-    <row r="86" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="33"/>
       <c r="B86" s="34">
         <v>74</v>
@@ -9463,7 +9460,7 @@
         <f t="shared" si="0"/>
         <v>74</v>
       </c>
-      <c r="X86" s="51" t="str">
+      <c r="X86" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9484,12 +9481,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD86" s="51" t="str">
+      <c r="AD86" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE86" s="52"/>
-      <c r="AF86" s="51" t="str">
+      <c r="AF86" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9510,18 +9507,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL86" s="51" t="str">
+      <c r="AL86" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM86" s="52"/>
-      <c r="AN86" s="51" t="str">
+      <c r="AN86" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO86" s="52"/>
     </row>
-    <row r="87" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="33"/>
       <c r="B87" s="34">
         <v>75</v>
@@ -9568,7 +9565,7 @@
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-      <c r="X87" s="53" t="str">
+      <c r="X87" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9589,12 +9586,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD87" s="53" t="str">
+      <c r="AD87" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE87" s="52"/>
-      <c r="AF87" s="53" t="str">
+      <c r="AF87" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9615,18 +9612,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL87" s="53" t="str">
+      <c r="AL87" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM87" s="52"/>
-      <c r="AN87" s="53" t="str">
+      <c r="AN87" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO87" s="52"/>
     </row>
-    <row r="88" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="33"/>
       <c r="B88" s="34">
         <v>76</v>
@@ -9673,7 +9670,7 @@
         <f t="shared" si="0"/>
         <v>76</v>
       </c>
-      <c r="X88" s="51" t="str">
+      <c r="X88" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9694,12 +9691,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD88" s="51" t="str">
+      <c r="AD88" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE88" s="52"/>
-      <c r="AF88" s="51" t="str">
+      <c r="AF88" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9720,18 +9717,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL88" s="51" t="str">
+      <c r="AL88" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM88" s="52"/>
-      <c r="AN88" s="51" t="str">
+      <c r="AN88" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO88" s="52"/>
     </row>
-    <row r="89" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="33"/>
       <c r="B89" s="34">
         <v>77</v>
@@ -9778,7 +9775,7 @@
         <f t="shared" si="0"/>
         <v>77</v>
       </c>
-      <c r="X89" s="53" t="str">
+      <c r="X89" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9799,12 +9796,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD89" s="53" t="str">
+      <c r="AD89" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE89" s="52"/>
-      <c r="AF89" s="53" t="str">
+      <c r="AF89" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9825,18 +9822,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL89" s="53" t="str">
+      <c r="AL89" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM89" s="52"/>
-      <c r="AN89" s="53" t="str">
+      <c r="AN89" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO89" s="52"/>
     </row>
-    <row r="90" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="33"/>
       <c r="B90" s="34">
         <v>78</v>
@@ -9883,7 +9880,7 @@
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-      <c r="X90" s="51" t="str">
+      <c r="X90" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -9904,12 +9901,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD90" s="51" t="str">
+      <c r="AD90" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE90" s="52"/>
-      <c r="AF90" s="51" t="str">
+      <c r="AF90" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -9930,18 +9927,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL90" s="51" t="str">
+      <c r="AL90" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM90" s="52"/>
-      <c r="AN90" s="51" t="str">
+      <c r="AN90" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO90" s="52"/>
     </row>
-    <row r="91" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="33"/>
       <c r="B91" s="34">
         <v>79</v>
@@ -9988,7 +9985,7 @@
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-      <c r="X91" s="53" t="str">
+      <c r="X91" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -10009,12 +10006,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD91" s="53" t="str">
+      <c r="AD91" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE91" s="52"/>
-      <c r="AF91" s="53" t="str">
+      <c r="AF91" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10035,18 +10032,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL91" s="53" t="str">
+      <c r="AL91" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM91" s="52"/>
-      <c r="AN91" s="53" t="str">
+      <c r="AN91" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO91" s="52"/>
     </row>
-    <row r="92" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="33"/>
       <c r="B92" s="34">
         <v>80</v>
@@ -10093,7 +10090,7 @@
         <f t="shared" si="0"/>
         <v>80</v>
       </c>
-      <c r="X92" s="51" t="str">
+      <c r="X92" s="53" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -10114,12 +10111,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD92" s="51" t="str">
+      <c r="AD92" s="53" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE92" s="52"/>
-      <c r="AF92" s="51" t="str">
+      <c r="AF92" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10140,18 +10137,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL92" s="51" t="str">
+      <c r="AL92" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM92" s="52"/>
-      <c r="AN92" s="51" t="str">
+      <c r="AN92" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO92" s="52"/>
     </row>
-    <row r="93" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="33"/>
       <c r="B93" s="34">
         <v>81</v>
@@ -10198,7 +10195,7 @@
         <f t="shared" si="0"/>
         <v>81</v>
       </c>
-      <c r="X93" s="53" t="str">
+      <c r="X93" s="51" t="str">
         <f t="shared" si="1"/>
         <v>Valid</v>
       </c>
@@ -10219,12 +10216,12 @@
         <f t="shared" si="5"/>
         <v>Valid</v>
       </c>
-      <c r="AD93" s="53" t="str">
+      <c r="AD93" s="51" t="str">
         <f t="shared" si="6"/>
         <v>Valid</v>
       </c>
       <c r="AE93" s="52"/>
-      <c r="AF93" s="53" t="str">
+      <c r="AF93" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10245,18 +10242,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL93" s="53" t="str">
+      <c r="AL93" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM93" s="52"/>
-      <c r="AN93" s="53" t="str">
+      <c r="AN93" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO93" s="52"/>
     </row>
-    <row r="94" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="33"/>
       <c r="B94" s="34">
         <v>82</v>
@@ -10285,7 +10282,7 @@
         <f t="shared" si="0"/>
         <v>82</v>
       </c>
-      <c r="X94" s="51" t="str">
+      <c r="X94" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10306,12 +10303,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD94" s="51" t="str">
+      <c r="AD94" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE94" s="52"/>
-      <c r="AF94" s="51" t="str">
+      <c r="AF94" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10332,18 +10329,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL94" s="51" t="str">
+      <c r="AL94" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM94" s="52"/>
-      <c r="AN94" s="51" t="str">
+      <c r="AN94" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO94" s="52"/>
     </row>
-    <row r="95" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="33"/>
       <c r="B95" s="34">
         <v>83</v>
@@ -10372,7 +10369,7 @@
         <f t="shared" si="0"/>
         <v>83</v>
       </c>
-      <c r="X95" s="53" t="str">
+      <c r="X95" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10393,12 +10390,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD95" s="53" t="str">
+      <c r="AD95" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE95" s="52"/>
-      <c r="AF95" s="53" t="str">
+      <c r="AF95" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10419,18 +10416,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL95" s="53" t="str">
+      <c r="AL95" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM95" s="52"/>
-      <c r="AN95" s="53" t="str">
+      <c r="AN95" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO95" s="52"/>
     </row>
-    <row r="96" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="33"/>
       <c r="B96" s="34">
         <v>84</v>
@@ -10459,7 +10456,7 @@
         <f t="shared" si="0"/>
         <v>84</v>
       </c>
-      <c r="X96" s="51" t="str">
+      <c r="X96" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10480,12 +10477,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD96" s="51" t="str">
+      <c r="AD96" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE96" s="52"/>
-      <c r="AF96" s="51" t="str">
+      <c r="AF96" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10506,18 +10503,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL96" s="51" t="str">
+      <c r="AL96" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM96" s="52"/>
-      <c r="AN96" s="51" t="str">
+      <c r="AN96" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO96" s="52"/>
     </row>
-    <row r="97" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="33"/>
       <c r="B97" s="34">
         <v>85</v>
@@ -10546,7 +10543,7 @@
         <f t="shared" si="0"/>
         <v>85</v>
       </c>
-      <c r="X97" s="53" t="str">
+      <c r="X97" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10567,12 +10564,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD97" s="53" t="str">
+      <c r="AD97" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE97" s="52"/>
-      <c r="AF97" s="53" t="str">
+      <c r="AF97" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10593,18 +10590,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL97" s="53" t="str">
+      <c r="AL97" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM97" s="52"/>
-      <c r="AN97" s="53" t="str">
+      <c r="AN97" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO97" s="52"/>
     </row>
-    <row r="98" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="33"/>
       <c r="B98" s="34">
         <v>86</v>
@@ -10633,7 +10630,7 @@
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-      <c r="X98" s="51" t="str">
+      <c r="X98" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10654,12 +10651,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD98" s="51" t="str">
+      <c r="AD98" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE98" s="52"/>
-      <c r="AF98" s="51" t="str">
+      <c r="AF98" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10680,18 +10677,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL98" s="51" t="str">
+      <c r="AL98" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM98" s="52"/>
-      <c r="AN98" s="51" t="str">
+      <c r="AN98" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO98" s="52"/>
     </row>
-    <row r="99" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="33"/>
       <c r="B99" s="34">
         <v>87</v>
@@ -10720,7 +10717,7 @@
         <f t="shared" si="0"/>
         <v>87</v>
       </c>
-      <c r="X99" s="53" t="str">
+      <c r="X99" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10741,12 +10738,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD99" s="53" t="str">
+      <c r="AD99" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE99" s="52"/>
-      <c r="AF99" s="53" t="str">
+      <c r="AF99" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10767,18 +10764,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL99" s="53" t="str">
+      <c r="AL99" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM99" s="52"/>
-      <c r="AN99" s="53" t="str">
+      <c r="AN99" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO99" s="52"/>
     </row>
-    <row r="100" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="33"/>
       <c r="B100" s="34">
         <v>88</v>
@@ -10807,7 +10804,7 @@
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-      <c r="X100" s="51" t="str">
+      <c r="X100" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10828,12 +10825,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD100" s="51" t="str">
+      <c r="AD100" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE100" s="52"/>
-      <c r="AF100" s="51" t="str">
+      <c r="AF100" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10854,18 +10851,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL100" s="51" t="str">
+      <c r="AL100" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM100" s="52"/>
-      <c r="AN100" s="51" t="str">
+      <c r="AN100" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO100" s="52"/>
     </row>
-    <row r="101" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="33"/>
       <c r="B101" s="34">
         <v>89</v>
@@ -10894,7 +10891,7 @@
         <f t="shared" si="0"/>
         <v>89</v>
       </c>
-      <c r="X101" s="53" t="str">
+      <c r="X101" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -10915,12 +10912,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD101" s="53" t="str">
+      <c r="AD101" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE101" s="52"/>
-      <c r="AF101" s="53" t="str">
+      <c r="AF101" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -10941,18 +10938,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL101" s="53" t="str">
+      <c r="AL101" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM101" s="52"/>
-      <c r="AN101" s="53" t="str">
+      <c r="AN101" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO101" s="52"/>
     </row>
-    <row r="102" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="33"/>
       <c r="B102" s="34">
         <v>90</v>
@@ -10981,7 +10978,7 @@
         <f t="shared" si="0"/>
         <v>90</v>
       </c>
-      <c r="X102" s="51" t="str">
+      <c r="X102" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11002,12 +10999,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD102" s="51" t="str">
+      <c r="AD102" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE102" s="52"/>
-      <c r="AF102" s="51" t="str">
+      <c r="AF102" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11028,18 +11025,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL102" s="51" t="str">
+      <c r="AL102" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM102" s="52"/>
-      <c r="AN102" s="51" t="str">
+      <c r="AN102" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO102" s="52"/>
     </row>
-    <row r="103" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="33"/>
       <c r="B103" s="34">
         <v>91</v>
@@ -11068,7 +11065,7 @@
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-      <c r="X103" s="53" t="str">
+      <c r="X103" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11089,12 +11086,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD103" s="53" t="str">
+      <c r="AD103" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE103" s="52"/>
-      <c r="AF103" s="53" t="str">
+      <c r="AF103" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11115,18 +11112,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL103" s="53" t="str">
+      <c r="AL103" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM103" s="52"/>
-      <c r="AN103" s="53" t="str">
+      <c r="AN103" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO103" s="52"/>
     </row>
-    <row r="104" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="33"/>
       <c r="B104" s="34">
         <v>92</v>
@@ -11155,7 +11152,7 @@
         <f t="shared" si="0"/>
         <v>92</v>
       </c>
-      <c r="X104" s="51" t="str">
+      <c r="X104" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11176,12 +11173,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD104" s="51" t="str">
+      <c r="AD104" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE104" s="52"/>
-      <c r="AF104" s="51" t="str">
+      <c r="AF104" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11202,18 +11199,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL104" s="51" t="str">
+      <c r="AL104" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM104" s="52"/>
-      <c r="AN104" s="51" t="str">
+      <c r="AN104" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO104" s="52"/>
     </row>
-    <row r="105" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="33"/>
       <c r="B105" s="34">
         <v>93</v>
@@ -11242,7 +11239,7 @@
         <f t="shared" si="0"/>
         <v>93</v>
       </c>
-      <c r="X105" s="53" t="str">
+      <c r="X105" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11263,12 +11260,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD105" s="53" t="str">
+      <c r="AD105" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE105" s="52"/>
-      <c r="AF105" s="53" t="str">
+      <c r="AF105" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11289,18 +11286,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL105" s="53" t="str">
+      <c r="AL105" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM105" s="52"/>
-      <c r="AN105" s="53" t="str">
+      <c r="AN105" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO105" s="52"/>
     </row>
-    <row r="106" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="33"/>
       <c r="B106" s="34">
         <v>94</v>
@@ -11329,7 +11326,7 @@
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-      <c r="X106" s="51" t="str">
+      <c r="X106" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11350,12 +11347,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD106" s="51" t="str">
+      <c r="AD106" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE106" s="52"/>
-      <c r="AF106" s="51" t="str">
+      <c r="AF106" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11376,18 +11373,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL106" s="51" t="str">
+      <c r="AL106" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM106" s="52"/>
-      <c r="AN106" s="51" t="str">
+      <c r="AN106" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO106" s="52"/>
     </row>
-    <row r="107" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="33"/>
       <c r="B107" s="34">
         <v>95</v>
@@ -11416,7 +11413,7 @@
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="X107" s="53" t="str">
+      <c r="X107" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11437,12 +11434,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD107" s="53" t="str">
+      <c r="AD107" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE107" s="52"/>
-      <c r="AF107" s="53" t="str">
+      <c r="AF107" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11463,18 +11460,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL107" s="53" t="str">
+      <c r="AL107" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM107" s="52"/>
-      <c r="AN107" s="53" t="str">
+      <c r="AN107" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO107" s="52"/>
     </row>
-    <row r="108" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="33"/>
       <c r="B108" s="34">
         <v>96</v>
@@ -11503,7 +11500,7 @@
         <f t="shared" si="0"/>
         <v>96</v>
       </c>
-      <c r="X108" s="51" t="str">
+      <c r="X108" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11524,12 +11521,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD108" s="51" t="str">
+      <c r="AD108" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE108" s="52"/>
-      <c r="AF108" s="51" t="str">
+      <c r="AF108" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11550,18 +11547,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL108" s="51" t="str">
+      <c r="AL108" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM108" s="52"/>
-      <c r="AN108" s="51" t="str">
+      <c r="AN108" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO108" s="52"/>
     </row>
-    <row r="109" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="33"/>
       <c r="B109" s="34">
         <v>97</v>
@@ -11590,7 +11587,7 @@
         <f t="shared" si="0"/>
         <v>97</v>
       </c>
-      <c r="X109" s="53" t="str">
+      <c r="X109" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11611,12 +11608,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD109" s="53" t="str">
+      <c r="AD109" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE109" s="52"/>
-      <c r="AF109" s="53" t="str">
+      <c r="AF109" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11637,18 +11634,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL109" s="53" t="str">
+      <c r="AL109" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM109" s="52"/>
-      <c r="AN109" s="53" t="str">
+      <c r="AN109" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO109" s="52"/>
     </row>
-    <row r="110" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33"/>
       <c r="B110" s="34">
         <v>98</v>
@@ -11677,7 +11674,7 @@
         <f t="shared" si="0"/>
         <v>98</v>
       </c>
-      <c r="X110" s="51" t="str">
+      <c r="X110" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11698,12 +11695,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD110" s="51" t="str">
+      <c r="AD110" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE110" s="52"/>
-      <c r="AF110" s="51" t="str">
+      <c r="AF110" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11724,18 +11721,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL110" s="51" t="str">
+      <c r="AL110" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM110" s="52"/>
-      <c r="AN110" s="51" t="str">
+      <c r="AN110" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO110" s="52"/>
     </row>
-    <row r="111" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="33"/>
       <c r="B111" s="34">
         <v>99</v>
@@ -11764,7 +11761,7 @@
         <f t="shared" si="0"/>
         <v>99</v>
       </c>
-      <c r="X111" s="53" t="str">
+      <c r="X111" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11785,12 +11782,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD111" s="53" t="str">
+      <c r="AD111" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE111" s="52"/>
-      <c r="AF111" s="53" t="str">
+      <c r="AF111" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11811,18 +11808,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL111" s="53" t="str">
+      <c r="AL111" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM111" s="52"/>
-      <c r="AN111" s="53" t="str">
+      <c r="AN111" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO111" s="52"/>
     </row>
-    <row r="112" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="33"/>
       <c r="B112" s="34">
         <v>100</v>
@@ -11851,7 +11848,7 @@
         <f t="shared" si="0"/>
         <v>100</v>
       </c>
-      <c r="X112" s="51" t="str">
+      <c r="X112" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11872,12 +11869,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD112" s="51" t="str">
+      <c r="AD112" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE112" s="52"/>
-      <c r="AF112" s="51" t="str">
+      <c r="AF112" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11898,18 +11895,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL112" s="51" t="str">
+      <c r="AL112" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM112" s="52"/>
-      <c r="AN112" s="51" t="str">
+      <c r="AN112" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO112" s="52"/>
     </row>
-    <row r="113" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="33"/>
       <c r="B113" s="34">
         <v>101</v>
@@ -11938,7 +11935,7 @@
         <f t="shared" si="0"/>
         <v>101</v>
       </c>
-      <c r="X113" s="53" t="str">
+      <c r="X113" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -11959,12 +11956,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD113" s="53" t="str">
+      <c r="AD113" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE113" s="52"/>
-      <c r="AF113" s="53" t="str">
+      <c r="AF113" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -11985,18 +11982,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL113" s="53" t="str">
+      <c r="AL113" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM113" s="52"/>
-      <c r="AN113" s="53" t="str">
+      <c r="AN113" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO113" s="52"/>
     </row>
-    <row r="114" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="33"/>
       <c r="B114" s="34">
         <v>102</v>
@@ -12025,7 +12022,7 @@
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-      <c r="X114" s="51" t="str">
+      <c r="X114" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12046,12 +12043,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD114" s="51" t="str">
+      <c r="AD114" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE114" s="52"/>
-      <c r="AF114" s="51" t="str">
+      <c r="AF114" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12072,18 +12069,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL114" s="51" t="str">
+      <c r="AL114" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM114" s="52"/>
-      <c r="AN114" s="51" t="str">
+      <c r="AN114" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO114" s="52"/>
     </row>
-    <row r="115" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="33"/>
       <c r="B115" s="34">
         <v>103</v>
@@ -12112,7 +12109,7 @@
         <f t="shared" si="0"/>
         <v>103</v>
       </c>
-      <c r="X115" s="53" t="str">
+      <c r="X115" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12133,12 +12130,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD115" s="53" t="str">
+      <c r="AD115" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE115" s="52"/>
-      <c r="AF115" s="53" t="str">
+      <c r="AF115" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12159,18 +12156,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL115" s="53" t="str">
+      <c r="AL115" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM115" s="52"/>
-      <c r="AN115" s="53" t="str">
+      <c r="AN115" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO115" s="52"/>
     </row>
-    <row r="116" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="33"/>
       <c r="B116" s="34">
         <v>104</v>
@@ -12199,7 +12196,7 @@
         <f t="shared" si="0"/>
         <v>104</v>
       </c>
-      <c r="X116" s="51" t="str">
+      <c r="X116" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12220,12 +12217,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD116" s="51" t="str">
+      <c r="AD116" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE116" s="52"/>
-      <c r="AF116" s="51" t="str">
+      <c r="AF116" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12246,18 +12243,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL116" s="51" t="str">
+      <c r="AL116" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM116" s="52"/>
-      <c r="AN116" s="51" t="str">
+      <c r="AN116" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO116" s="52"/>
     </row>
-    <row r="117" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="33"/>
       <c r="B117" s="34">
         <v>105</v>
@@ -12286,7 +12283,7 @@
         <f t="shared" si="0"/>
         <v>105</v>
       </c>
-      <c r="X117" s="53" t="str">
+      <c r="X117" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12307,12 +12304,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD117" s="53" t="str">
+      <c r="AD117" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE117" s="52"/>
-      <c r="AF117" s="53" t="str">
+      <c r="AF117" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12333,18 +12330,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL117" s="53" t="str">
+      <c r="AL117" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM117" s="52"/>
-      <c r="AN117" s="53" t="str">
+      <c r="AN117" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO117" s="52"/>
     </row>
-    <row r="118" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="33"/>
       <c r="B118" s="34">
         <v>106</v>
@@ -12373,7 +12370,7 @@
         <f t="shared" si="0"/>
         <v>106</v>
       </c>
-      <c r="X118" s="51" t="str">
+      <c r="X118" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12394,12 +12391,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD118" s="51" t="str">
+      <c r="AD118" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE118" s="52"/>
-      <c r="AF118" s="51" t="str">
+      <c r="AF118" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12420,18 +12417,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL118" s="51" t="str">
+      <c r="AL118" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM118" s="52"/>
-      <c r="AN118" s="51" t="str">
+      <c r="AN118" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO118" s="52"/>
     </row>
-    <row r="119" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="33"/>
       <c r="B119" s="34">
         <v>107</v>
@@ -12460,7 +12457,7 @@
         <f t="shared" si="0"/>
         <v>107</v>
       </c>
-      <c r="X119" s="53" t="str">
+      <c r="X119" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12481,12 +12478,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD119" s="53" t="str">
+      <c r="AD119" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE119" s="52"/>
-      <c r="AF119" s="53" t="str">
+      <c r="AF119" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12507,18 +12504,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL119" s="53" t="str">
+      <c r="AL119" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM119" s="52"/>
-      <c r="AN119" s="53" t="str">
+      <c r="AN119" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO119" s="52"/>
     </row>
-    <row r="120" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="33"/>
       <c r="B120" s="34">
         <v>108</v>
@@ -12547,7 +12544,7 @@
         <f t="shared" si="0"/>
         <v>108</v>
       </c>
-      <c r="X120" s="51" t="str">
+      <c r="X120" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12568,12 +12565,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD120" s="51" t="str">
+      <c r="AD120" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE120" s="52"/>
-      <c r="AF120" s="51" t="str">
+      <c r="AF120" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12594,18 +12591,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL120" s="51" t="str">
+      <c r="AL120" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM120" s="52"/>
-      <c r="AN120" s="51" t="str">
+      <c r="AN120" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO120" s="52"/>
     </row>
-    <row r="121" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="33"/>
       <c r="B121" s="34">
         <v>109</v>
@@ -12634,7 +12631,7 @@
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-      <c r="X121" s="53" t="str">
+      <c r="X121" s="51" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12655,12 +12652,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD121" s="53" t="str">
+      <c r="AD121" s="51" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE121" s="52"/>
-      <c r="AF121" s="53" t="str">
+      <c r="AF121" s="51" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12681,18 +12678,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL121" s="53" t="str">
+      <c r="AL121" s="51" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM121" s="52"/>
-      <c r="AN121" s="53" t="str">
+      <c r="AN121" s="51" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO121" s="52"/>
     </row>
-    <row r="122" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:41" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="33"/>
       <c r="B122" s="44">
         <v>110</v>
@@ -12721,7 +12718,7 @@
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-      <c r="X122" s="51" t="str">
+      <c r="X122" s="53" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -12742,12 +12739,12 @@
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="AD122" s="51" t="str">
+      <c r="AD122" s="53" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
       <c r="AE122" s="52"/>
-      <c r="AF122" s="51" t="str">
+      <c r="AF122" s="53" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
@@ -12768,18 +12765,18 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AL122" s="51" t="str">
+      <c r="AL122" s="53" t="str">
         <f t="shared" si="12"/>
         <v/>
       </c>
       <c r="AM122" s="52"/>
-      <c r="AN122" s="51" t="str">
+      <c r="AN122" s="53" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
       <c r="AO122" s="52"/>
     </row>
-    <row r="123" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="33"/>
       <c r="B123" s="49"/>
       <c r="C123" s="33"/>
@@ -12824,39 +12821,521 @@
     </row>
   </sheetData>
   <mergeCells count="572">
-    <mergeCell ref="AL97:AM97"/>
-    <mergeCell ref="AL98:AM98"/>
-    <mergeCell ref="AL99:AM99"/>
-    <mergeCell ref="AN99:AO99"/>
-    <mergeCell ref="AL100:AM100"/>
-    <mergeCell ref="AN100:AO100"/>
-    <mergeCell ref="AN89:AO89"/>
-    <mergeCell ref="AL89:AM89"/>
-    <mergeCell ref="AL90:AM90"/>
-    <mergeCell ref="AL91:AM91"/>
-    <mergeCell ref="AL92:AM92"/>
-    <mergeCell ref="AL93:AM93"/>
-    <mergeCell ref="AL94:AM94"/>
-    <mergeCell ref="AL95:AM95"/>
-    <mergeCell ref="AL96:AM96"/>
-    <mergeCell ref="AL86:AM86"/>
-    <mergeCell ref="AL87:AM87"/>
-    <mergeCell ref="AL88:AM88"/>
-    <mergeCell ref="AN83:AO83"/>
-    <mergeCell ref="AN84:AO84"/>
-    <mergeCell ref="AN85:AO85"/>
-    <mergeCell ref="AN86:AO86"/>
-    <mergeCell ref="AN87:AO87"/>
-    <mergeCell ref="AN88:AO88"/>
-    <mergeCell ref="AN78:AO78"/>
-    <mergeCell ref="AN79:AO79"/>
-    <mergeCell ref="AN80:AO80"/>
-    <mergeCell ref="AN81:AO81"/>
-    <mergeCell ref="AN82:AO82"/>
-    <mergeCell ref="AL82:AM82"/>
-    <mergeCell ref="AL83:AM83"/>
-    <mergeCell ref="AL84:AM84"/>
-    <mergeCell ref="AL85:AM85"/>
+    <mergeCell ref="AN40:AO40"/>
+    <mergeCell ref="AN32:AO32"/>
+    <mergeCell ref="AN33:AO33"/>
+    <mergeCell ref="AN34:AO34"/>
+    <mergeCell ref="AN35:AO35"/>
+    <mergeCell ref="AN36:AO36"/>
+    <mergeCell ref="AN37:AO37"/>
+    <mergeCell ref="AN38:AO38"/>
+    <mergeCell ref="AD23:AE23"/>
+    <mergeCell ref="AF23:AG23"/>
+    <mergeCell ref="AL23:AM23"/>
+    <mergeCell ref="AN23:AO23"/>
+    <mergeCell ref="AL33:AM33"/>
+    <mergeCell ref="AL34:AM34"/>
+    <mergeCell ref="AL35:AM35"/>
+    <mergeCell ref="AL36:AM36"/>
+    <mergeCell ref="AL37:AM37"/>
+    <mergeCell ref="AL38:AM38"/>
+    <mergeCell ref="AL39:AM39"/>
+    <mergeCell ref="AL40:AM40"/>
+    <mergeCell ref="AD31:AE31"/>
+    <mergeCell ref="AF31:AG31"/>
+    <mergeCell ref="AD32:AE32"/>
+    <mergeCell ref="AF32:AG32"/>
+    <mergeCell ref="X23:Y23"/>
+    <mergeCell ref="AD24:AE24"/>
+    <mergeCell ref="AF24:AG24"/>
+    <mergeCell ref="AN24:AO24"/>
+    <mergeCell ref="AN39:AO39"/>
+    <mergeCell ref="AN28:AO28"/>
+    <mergeCell ref="AL29:AM29"/>
+    <mergeCell ref="AN29:AO29"/>
+    <mergeCell ref="AL30:AM30"/>
+    <mergeCell ref="AN30:AO30"/>
+    <mergeCell ref="AD25:AE25"/>
+    <mergeCell ref="AF25:AG25"/>
+    <mergeCell ref="AN25:AO25"/>
+    <mergeCell ref="AD26:AE26"/>
+    <mergeCell ref="AF26:AG26"/>
+    <mergeCell ref="AL26:AM26"/>
+    <mergeCell ref="AN26:AO26"/>
+    <mergeCell ref="AF27:AG27"/>
+    <mergeCell ref="AL27:AM27"/>
+    <mergeCell ref="AN27:AO27"/>
+    <mergeCell ref="AD27:AE27"/>
+    <mergeCell ref="AN31:AO31"/>
+    <mergeCell ref="AL31:AM31"/>
+    <mergeCell ref="AL32:AM32"/>
+    <mergeCell ref="AL41:AM41"/>
+    <mergeCell ref="AN41:AO41"/>
+    <mergeCell ref="AL42:AM42"/>
+    <mergeCell ref="AN42:AO42"/>
+    <mergeCell ref="AF56:AG56"/>
+    <mergeCell ref="AF57:AG57"/>
+    <mergeCell ref="AF49:AG49"/>
+    <mergeCell ref="AF50:AG50"/>
+    <mergeCell ref="AF51:AG51"/>
+    <mergeCell ref="AF52:AG52"/>
+    <mergeCell ref="AF53:AG53"/>
+    <mergeCell ref="AF54:AG54"/>
+    <mergeCell ref="AF55:AG55"/>
+    <mergeCell ref="AF41:AG41"/>
+    <mergeCell ref="AF48:AG48"/>
+    <mergeCell ref="AL43:AM43"/>
+    <mergeCell ref="AN43:AO43"/>
+    <mergeCell ref="AL44:AM44"/>
+    <mergeCell ref="AN44:AO44"/>
+    <mergeCell ref="AL45:AM45"/>
+    <mergeCell ref="AN45:AO45"/>
+    <mergeCell ref="AN46:AO46"/>
+    <mergeCell ref="AL46:AM46"/>
+    <mergeCell ref="AL47:AM47"/>
+    <mergeCell ref="AD33:AE33"/>
+    <mergeCell ref="AF33:AG33"/>
+    <mergeCell ref="AF34:AG34"/>
+    <mergeCell ref="AD34:AE34"/>
+    <mergeCell ref="AD35:AE35"/>
+    <mergeCell ref="AD36:AE36"/>
+    <mergeCell ref="AD37:AE37"/>
+    <mergeCell ref="AD38:AE38"/>
+    <mergeCell ref="AD39:AE39"/>
+    <mergeCell ref="AD40:AE40"/>
+    <mergeCell ref="AF35:AG35"/>
+    <mergeCell ref="AF36:AG36"/>
+    <mergeCell ref="AF37:AG37"/>
+    <mergeCell ref="AF38:AG38"/>
+    <mergeCell ref="AF39:AG39"/>
+    <mergeCell ref="AF40:AG40"/>
+    <mergeCell ref="AD41:AE41"/>
+    <mergeCell ref="AD42:AE42"/>
+    <mergeCell ref="AD43:AE43"/>
+    <mergeCell ref="AD44:AE44"/>
+    <mergeCell ref="AD45:AE45"/>
+    <mergeCell ref="AD46:AE46"/>
+    <mergeCell ref="AD47:AE47"/>
+    <mergeCell ref="AF42:AG42"/>
+    <mergeCell ref="AF43:AG43"/>
+    <mergeCell ref="AF44:AG44"/>
+    <mergeCell ref="AF45:AG45"/>
+    <mergeCell ref="AF46:AG46"/>
+    <mergeCell ref="AF47:AG47"/>
+    <mergeCell ref="AD48:AE48"/>
+    <mergeCell ref="AD49:AE49"/>
+    <mergeCell ref="AD50:AE50"/>
+    <mergeCell ref="AD51:AE51"/>
+    <mergeCell ref="AD52:AE52"/>
+    <mergeCell ref="AD53:AE53"/>
+    <mergeCell ref="AD54:AE54"/>
+    <mergeCell ref="AD55:AE55"/>
+    <mergeCell ref="AD56:AE56"/>
+    <mergeCell ref="AD57:AE57"/>
+    <mergeCell ref="AD58:AE58"/>
+    <mergeCell ref="AF58:AG58"/>
+    <mergeCell ref="AD59:AE59"/>
+    <mergeCell ref="AF59:AG59"/>
+    <mergeCell ref="AN68:AO68"/>
+    <mergeCell ref="AN69:AO69"/>
+    <mergeCell ref="AN61:AO61"/>
+    <mergeCell ref="AN62:AO62"/>
+    <mergeCell ref="AN63:AO63"/>
+    <mergeCell ref="AN64:AO64"/>
+    <mergeCell ref="AN65:AO65"/>
+    <mergeCell ref="AN66:AO66"/>
+    <mergeCell ref="AN67:AO67"/>
+    <mergeCell ref="AN60:AO60"/>
+    <mergeCell ref="AL60:AM60"/>
+    <mergeCell ref="AL61:AM61"/>
+    <mergeCell ref="AL62:AM62"/>
+    <mergeCell ref="AL63:AM63"/>
+    <mergeCell ref="AL64:AM64"/>
+    <mergeCell ref="AL65:AM65"/>
+    <mergeCell ref="AL66:AM66"/>
+    <mergeCell ref="AL67:AM67"/>
+    <mergeCell ref="AL68:AM68"/>
+    <mergeCell ref="AL48:AM48"/>
+    <mergeCell ref="AL49:AM49"/>
+    <mergeCell ref="AL50:AM50"/>
+    <mergeCell ref="AL51:AM51"/>
+    <mergeCell ref="AL52:AM52"/>
+    <mergeCell ref="AN47:AO47"/>
+    <mergeCell ref="AN48:AO48"/>
+    <mergeCell ref="AN49:AO49"/>
+    <mergeCell ref="AN50:AO50"/>
+    <mergeCell ref="AN51:AO51"/>
+    <mergeCell ref="AN52:AO52"/>
+    <mergeCell ref="AN53:AO53"/>
+    <mergeCell ref="AL53:AM53"/>
+    <mergeCell ref="AL54:AM54"/>
+    <mergeCell ref="AL55:AM55"/>
+    <mergeCell ref="AL56:AM56"/>
+    <mergeCell ref="AL57:AM57"/>
+    <mergeCell ref="AL58:AM58"/>
+    <mergeCell ref="AL59:AM59"/>
+    <mergeCell ref="AN54:AO54"/>
+    <mergeCell ref="AN55:AO55"/>
+    <mergeCell ref="AN56:AO56"/>
+    <mergeCell ref="AN57:AO57"/>
+    <mergeCell ref="AN58:AO58"/>
+    <mergeCell ref="AN59:AO59"/>
+    <mergeCell ref="AL69:AM69"/>
+    <mergeCell ref="AL70:AM70"/>
+    <mergeCell ref="AN70:AO70"/>
+    <mergeCell ref="AL71:AM71"/>
+    <mergeCell ref="AN71:AO71"/>
+    <mergeCell ref="AF85:AG85"/>
+    <mergeCell ref="AF86:AG86"/>
+    <mergeCell ref="AF78:AG78"/>
+    <mergeCell ref="AF79:AG79"/>
+    <mergeCell ref="AF80:AG80"/>
+    <mergeCell ref="AF81:AG81"/>
+    <mergeCell ref="AF82:AG82"/>
+    <mergeCell ref="AF83:AG83"/>
+    <mergeCell ref="AF84:AG84"/>
+    <mergeCell ref="AF70:AG70"/>
+    <mergeCell ref="AF77:AG77"/>
+    <mergeCell ref="AL76:AM76"/>
+    <mergeCell ref="AL77:AM77"/>
+    <mergeCell ref="AL78:AM78"/>
+    <mergeCell ref="AL79:AM79"/>
+    <mergeCell ref="AL80:AM80"/>
+    <mergeCell ref="AL81:AM81"/>
+    <mergeCell ref="AN76:AO76"/>
+    <mergeCell ref="AN77:AO77"/>
+    <mergeCell ref="AF64:AG64"/>
+    <mergeCell ref="AF65:AG65"/>
+    <mergeCell ref="AF66:AG66"/>
+    <mergeCell ref="AF67:AG67"/>
+    <mergeCell ref="AF68:AG68"/>
+    <mergeCell ref="AF69:AG69"/>
+    <mergeCell ref="AD60:AE60"/>
+    <mergeCell ref="AF60:AG60"/>
+    <mergeCell ref="AD61:AE61"/>
+    <mergeCell ref="AF61:AG61"/>
+    <mergeCell ref="AD62:AE62"/>
+    <mergeCell ref="AF62:AG62"/>
+    <mergeCell ref="AF63:AG63"/>
+    <mergeCell ref="AD63:AE63"/>
+    <mergeCell ref="AD64:AE64"/>
+    <mergeCell ref="AF71:AG71"/>
+    <mergeCell ref="AF72:AG72"/>
+    <mergeCell ref="AF73:AG73"/>
+    <mergeCell ref="AF74:AG74"/>
+    <mergeCell ref="AF75:AG75"/>
+    <mergeCell ref="AF76:AG76"/>
+    <mergeCell ref="AD65:AE65"/>
+    <mergeCell ref="AD66:AE66"/>
+    <mergeCell ref="AD67:AE67"/>
+    <mergeCell ref="AD68:AE68"/>
+    <mergeCell ref="AD69:AE69"/>
+    <mergeCell ref="AD77:AE77"/>
+    <mergeCell ref="AD78:AE78"/>
+    <mergeCell ref="AD79:AE79"/>
+    <mergeCell ref="AD80:AE80"/>
+    <mergeCell ref="AD81:AE81"/>
+    <mergeCell ref="AD82:AE82"/>
+    <mergeCell ref="AD83:AE83"/>
+    <mergeCell ref="AD70:AE70"/>
+    <mergeCell ref="AD71:AE71"/>
+    <mergeCell ref="AD72:AE72"/>
+    <mergeCell ref="AD73:AE73"/>
+    <mergeCell ref="AD74:AE74"/>
+    <mergeCell ref="AD75:AE75"/>
+    <mergeCell ref="AD76:AE76"/>
+    <mergeCell ref="AF98:AG98"/>
+    <mergeCell ref="AF99:AG99"/>
+    <mergeCell ref="AF91:AG91"/>
+    <mergeCell ref="AF92:AG92"/>
+    <mergeCell ref="AF93:AG93"/>
+    <mergeCell ref="AF94:AG94"/>
+    <mergeCell ref="AF95:AG95"/>
+    <mergeCell ref="AF96:AG96"/>
+    <mergeCell ref="AF97:AG97"/>
+    <mergeCell ref="AF100:AG100"/>
+    <mergeCell ref="AD101:AE101"/>
+    <mergeCell ref="AF101:AG101"/>
+    <mergeCell ref="AD102:AE102"/>
+    <mergeCell ref="AF102:AG102"/>
+    <mergeCell ref="X120:Y120"/>
+    <mergeCell ref="X121:Y121"/>
+    <mergeCell ref="X122:Y122"/>
+    <mergeCell ref="X109:Y109"/>
+    <mergeCell ref="X110:Y110"/>
+    <mergeCell ref="X111:Y111"/>
+    <mergeCell ref="X112:Y112"/>
+    <mergeCell ref="X113:Y113"/>
+    <mergeCell ref="X114:Y114"/>
+    <mergeCell ref="X115:Y115"/>
+    <mergeCell ref="X104:Y104"/>
+    <mergeCell ref="X105:Y105"/>
+    <mergeCell ref="X106:Y106"/>
+    <mergeCell ref="X107:Y107"/>
+    <mergeCell ref="X108:Y108"/>
+    <mergeCell ref="X116:Y116"/>
+    <mergeCell ref="X117:Y117"/>
+    <mergeCell ref="X118:Y118"/>
+    <mergeCell ref="X119:Y119"/>
+    <mergeCell ref="AF103:AG103"/>
+    <mergeCell ref="AD104:AE104"/>
+    <mergeCell ref="AF104:AG104"/>
+    <mergeCell ref="AF105:AG105"/>
+    <mergeCell ref="AF113:AG113"/>
+    <mergeCell ref="AF114:AG114"/>
+    <mergeCell ref="AF106:AG106"/>
+    <mergeCell ref="AF107:AG107"/>
+    <mergeCell ref="AF108:AG108"/>
+    <mergeCell ref="AF109:AG109"/>
+    <mergeCell ref="AF110:AG110"/>
+    <mergeCell ref="AF111:AG111"/>
+    <mergeCell ref="AF112:AG112"/>
+    <mergeCell ref="AD106:AE106"/>
+    <mergeCell ref="AD107:AE107"/>
+    <mergeCell ref="AD108:AE108"/>
+    <mergeCell ref="AD109:AE109"/>
+    <mergeCell ref="AD110:AE110"/>
+    <mergeCell ref="AD111:AE111"/>
+    <mergeCell ref="AD112:AE112"/>
+    <mergeCell ref="AD113:AE113"/>
+    <mergeCell ref="AD114:AE114"/>
+    <mergeCell ref="AD120:AE120"/>
+    <mergeCell ref="AD121:AE121"/>
+    <mergeCell ref="AD122:AE122"/>
+    <mergeCell ref="AF121:AG121"/>
+    <mergeCell ref="AF122:AG122"/>
+    <mergeCell ref="AD117:AE117"/>
+    <mergeCell ref="AF117:AG117"/>
+    <mergeCell ref="AD118:AE118"/>
+    <mergeCell ref="AF118:AG118"/>
+    <mergeCell ref="AD119:AE119"/>
+    <mergeCell ref="AF119:AG119"/>
+    <mergeCell ref="AF120:AG120"/>
+    <mergeCell ref="X74:Y74"/>
+    <mergeCell ref="X75:Y75"/>
+    <mergeCell ref="X76:Y76"/>
+    <mergeCell ref="X77:Y77"/>
+    <mergeCell ref="X78:Y78"/>
+    <mergeCell ref="X79:Y79"/>
+    <mergeCell ref="X80:Y80"/>
+    <mergeCell ref="X81:Y81"/>
+    <mergeCell ref="X82:Y82"/>
+    <mergeCell ref="X83:Y83"/>
+    <mergeCell ref="X84:Y84"/>
+    <mergeCell ref="X85:Y85"/>
+    <mergeCell ref="X86:Y86"/>
+    <mergeCell ref="X87:Y87"/>
+    <mergeCell ref="AD87:AE87"/>
+    <mergeCell ref="AF87:AG87"/>
+    <mergeCell ref="AD88:AE88"/>
+    <mergeCell ref="AF88:AG88"/>
+    <mergeCell ref="AD84:AE84"/>
+    <mergeCell ref="AD85:AE85"/>
+    <mergeCell ref="AD86:AE86"/>
+    <mergeCell ref="AD89:AE89"/>
+    <mergeCell ref="AF89:AG89"/>
+    <mergeCell ref="AF90:AG90"/>
+    <mergeCell ref="X88:Y88"/>
+    <mergeCell ref="X89:Y89"/>
+    <mergeCell ref="X90:Y90"/>
+    <mergeCell ref="X91:Y91"/>
+    <mergeCell ref="X92:Y92"/>
+    <mergeCell ref="X93:Y93"/>
+    <mergeCell ref="X94:Y94"/>
+    <mergeCell ref="AD90:AE90"/>
+    <mergeCell ref="AD91:AE91"/>
+    <mergeCell ref="AD92:AE92"/>
+    <mergeCell ref="AD93:AE93"/>
+    <mergeCell ref="AD94:AE94"/>
+    <mergeCell ref="AD95:AE95"/>
+    <mergeCell ref="AD96:AE96"/>
+    <mergeCell ref="AD105:AE105"/>
+    <mergeCell ref="AD103:AE103"/>
+    <mergeCell ref="AD97:AE97"/>
+    <mergeCell ref="AD98:AE98"/>
+    <mergeCell ref="AD99:AE99"/>
+    <mergeCell ref="AD100:AE100"/>
+    <mergeCell ref="X95:Y95"/>
+    <mergeCell ref="X96:Y96"/>
+    <mergeCell ref="X97:Y97"/>
+    <mergeCell ref="X98:Y98"/>
+    <mergeCell ref="X99:Y99"/>
+    <mergeCell ref="X100:Y100"/>
+    <mergeCell ref="X101:Y101"/>
+    <mergeCell ref="X102:Y102"/>
+    <mergeCell ref="X103:Y103"/>
+    <mergeCell ref="AD115:AE115"/>
+    <mergeCell ref="AF115:AG115"/>
+    <mergeCell ref="AD116:AE116"/>
+    <mergeCell ref="AF116:AG116"/>
+    <mergeCell ref="AL17:AM17"/>
+    <mergeCell ref="AL18:AM18"/>
+    <mergeCell ref="AL14:AM14"/>
+    <mergeCell ref="AN14:AO14"/>
+    <mergeCell ref="AL15:AM15"/>
+    <mergeCell ref="AN15:AO15"/>
+    <mergeCell ref="AL16:AM16"/>
+    <mergeCell ref="AN16:AO16"/>
+    <mergeCell ref="AN17:AO17"/>
+    <mergeCell ref="AN18:AO18"/>
+    <mergeCell ref="AD19:AE19"/>
+    <mergeCell ref="AD20:AE20"/>
+    <mergeCell ref="AF20:AG20"/>
+    <mergeCell ref="AD17:AE17"/>
+    <mergeCell ref="AF17:AG17"/>
+    <mergeCell ref="AD18:AE18"/>
+    <mergeCell ref="AF18:AG18"/>
+    <mergeCell ref="AF19:AG19"/>
+    <mergeCell ref="AL19:AM19"/>
+    <mergeCell ref="AN19:AO19"/>
+    <mergeCell ref="AL21:AM21"/>
+    <mergeCell ref="AL22:AM22"/>
+    <mergeCell ref="AL20:AM20"/>
+    <mergeCell ref="AN20:AO20"/>
+    <mergeCell ref="AD21:AE21"/>
+    <mergeCell ref="AF21:AG21"/>
+    <mergeCell ref="AN21:AO21"/>
+    <mergeCell ref="AF22:AG22"/>
+    <mergeCell ref="AN22:AO22"/>
+    <mergeCell ref="AD22:AE22"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="R4:S4"/>
+    <mergeCell ref="E7:G7"/>
+    <mergeCell ref="H7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="N7:P7"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="E9:G9"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="K9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="Q9:S9"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="J11:K11"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="R11:S11"/>
+    <mergeCell ref="T11:U11"/>
+    <mergeCell ref="AD11:AE11"/>
+    <mergeCell ref="AF11:AG11"/>
+    <mergeCell ref="AL11:AM11"/>
+    <mergeCell ref="AN11:AO11"/>
+    <mergeCell ref="X11:Y11"/>
+    <mergeCell ref="X13:Y13"/>
+    <mergeCell ref="AD13:AE13"/>
+    <mergeCell ref="AF13:AG13"/>
+    <mergeCell ref="AL13:AM13"/>
+    <mergeCell ref="AN13:AO13"/>
+    <mergeCell ref="X14:Y14"/>
+    <mergeCell ref="AD14:AE14"/>
+    <mergeCell ref="AF14:AG14"/>
+    <mergeCell ref="X15:Y15"/>
+    <mergeCell ref="AD15:AE15"/>
+    <mergeCell ref="AF15:AG15"/>
+    <mergeCell ref="AD16:AE16"/>
+    <mergeCell ref="AF16:AG16"/>
+    <mergeCell ref="X16:Y16"/>
+    <mergeCell ref="X17:Y17"/>
+    <mergeCell ref="X18:Y18"/>
+    <mergeCell ref="X19:Y19"/>
+    <mergeCell ref="X20:Y20"/>
+    <mergeCell ref="X21:Y21"/>
+    <mergeCell ref="X22:Y22"/>
+    <mergeCell ref="X25:Y25"/>
+    <mergeCell ref="AL24:AM24"/>
+    <mergeCell ref="AL25:AM25"/>
+    <mergeCell ref="X24:Y24"/>
+    <mergeCell ref="X26:Y26"/>
+    <mergeCell ref="X27:Y27"/>
+    <mergeCell ref="X28:Y28"/>
+    <mergeCell ref="X29:Y29"/>
+    <mergeCell ref="X30:Y30"/>
+    <mergeCell ref="AD28:AE28"/>
+    <mergeCell ref="AF28:AG28"/>
+    <mergeCell ref="AD29:AE29"/>
+    <mergeCell ref="AF29:AG29"/>
+    <mergeCell ref="AD30:AE30"/>
+    <mergeCell ref="AF30:AG30"/>
+    <mergeCell ref="AL28:AM28"/>
+    <mergeCell ref="X31:Y31"/>
+    <mergeCell ref="X32:Y32"/>
+    <mergeCell ref="X33:Y33"/>
+    <mergeCell ref="X34:Y34"/>
+    <mergeCell ref="X35:Y35"/>
+    <mergeCell ref="X36:Y36"/>
+    <mergeCell ref="X37:Y37"/>
+    <mergeCell ref="X38:Y38"/>
+    <mergeCell ref="X39:Y39"/>
+    <mergeCell ref="X40:Y40"/>
+    <mergeCell ref="X41:Y41"/>
+    <mergeCell ref="X42:Y42"/>
+    <mergeCell ref="X43:Y43"/>
+    <mergeCell ref="X44:Y44"/>
+    <mergeCell ref="X45:Y45"/>
+    <mergeCell ref="X46:Y46"/>
+    <mergeCell ref="X47:Y47"/>
+    <mergeCell ref="X48:Y48"/>
+    <mergeCell ref="X49:Y49"/>
+    <mergeCell ref="X50:Y50"/>
+    <mergeCell ref="X51:Y51"/>
+    <mergeCell ref="X52:Y52"/>
+    <mergeCell ref="X53:Y53"/>
+    <mergeCell ref="X54:Y54"/>
+    <mergeCell ref="X55:Y55"/>
+    <mergeCell ref="X56:Y56"/>
+    <mergeCell ref="X57:Y57"/>
+    <mergeCell ref="X58:Y58"/>
+    <mergeCell ref="X59:Y59"/>
+    <mergeCell ref="X60:Y60"/>
+    <mergeCell ref="X61:Y61"/>
+    <mergeCell ref="X62:Y62"/>
+    <mergeCell ref="X63:Y63"/>
+    <mergeCell ref="X64:Y64"/>
+    <mergeCell ref="X65:Y65"/>
+    <mergeCell ref="X66:Y66"/>
+    <mergeCell ref="X67:Y67"/>
+    <mergeCell ref="X68:Y68"/>
+    <mergeCell ref="X69:Y69"/>
+    <mergeCell ref="X70:Y70"/>
+    <mergeCell ref="X71:Y71"/>
+    <mergeCell ref="X72:Y72"/>
+    <mergeCell ref="X73:Y73"/>
+    <mergeCell ref="AN97:AO97"/>
+    <mergeCell ref="AN98:AO98"/>
+    <mergeCell ref="AN90:AO90"/>
+    <mergeCell ref="AN91:AO91"/>
+    <mergeCell ref="AN92:AO92"/>
+    <mergeCell ref="AN93:AO93"/>
+    <mergeCell ref="AN94:AO94"/>
+    <mergeCell ref="AN95:AO95"/>
+    <mergeCell ref="AN96:AO96"/>
+    <mergeCell ref="AL72:AM72"/>
+    <mergeCell ref="AN72:AO72"/>
+    <mergeCell ref="AL73:AM73"/>
+    <mergeCell ref="AN73:AO73"/>
+    <mergeCell ref="AL74:AM74"/>
+    <mergeCell ref="AN74:AO74"/>
+    <mergeCell ref="AN75:AO75"/>
+    <mergeCell ref="AL75:AM75"/>
+    <mergeCell ref="AL101:AM101"/>
+    <mergeCell ref="AN101:AO101"/>
+    <mergeCell ref="AL102:AM102"/>
+    <mergeCell ref="AN102:AO102"/>
+    <mergeCell ref="AL103:AM103"/>
+    <mergeCell ref="AN103:AO103"/>
+    <mergeCell ref="AN104:AO104"/>
+    <mergeCell ref="AL104:AM104"/>
+    <mergeCell ref="AL105:AM105"/>
+    <mergeCell ref="AL106:AM106"/>
+    <mergeCell ref="AL107:AM107"/>
+    <mergeCell ref="AL108:AM108"/>
+    <mergeCell ref="AL109:AM109"/>
+    <mergeCell ref="AL110:AM110"/>
+    <mergeCell ref="AN105:AO105"/>
+    <mergeCell ref="AN106:AO106"/>
+    <mergeCell ref="AN107:AO107"/>
+    <mergeCell ref="AN108:AO108"/>
+    <mergeCell ref="AN109:AO109"/>
+    <mergeCell ref="AN110:AO110"/>
     <mergeCell ref="AN111:AO111"/>
     <mergeCell ref="AL118:AM118"/>
     <mergeCell ref="AL119:AM119"/>
@@ -12881,521 +13360,39 @@
     <mergeCell ref="AN116:AO116"/>
     <mergeCell ref="AN117:AO117"/>
     <mergeCell ref="AN118:AO118"/>
-    <mergeCell ref="AL106:AM106"/>
-    <mergeCell ref="AL107:AM107"/>
-    <mergeCell ref="AL108:AM108"/>
-    <mergeCell ref="AL109:AM109"/>
-    <mergeCell ref="AL110:AM110"/>
-    <mergeCell ref="AN105:AO105"/>
-    <mergeCell ref="AN106:AO106"/>
-    <mergeCell ref="AN107:AO107"/>
-    <mergeCell ref="AN108:AO108"/>
-    <mergeCell ref="AN109:AO109"/>
-    <mergeCell ref="AN110:AO110"/>
-    <mergeCell ref="AL101:AM101"/>
-    <mergeCell ref="AN101:AO101"/>
-    <mergeCell ref="AL102:AM102"/>
-    <mergeCell ref="AN102:AO102"/>
-    <mergeCell ref="AL103:AM103"/>
-    <mergeCell ref="AN103:AO103"/>
-    <mergeCell ref="AN104:AO104"/>
-    <mergeCell ref="AL104:AM104"/>
-    <mergeCell ref="AL105:AM105"/>
-    <mergeCell ref="X67:Y67"/>
-    <mergeCell ref="X68:Y68"/>
-    <mergeCell ref="X69:Y69"/>
-    <mergeCell ref="X70:Y70"/>
-    <mergeCell ref="X71:Y71"/>
-    <mergeCell ref="X72:Y72"/>
-    <mergeCell ref="X73:Y73"/>
-    <mergeCell ref="AN97:AO97"/>
-    <mergeCell ref="AN98:AO98"/>
-    <mergeCell ref="AN90:AO90"/>
-    <mergeCell ref="AN91:AO91"/>
-    <mergeCell ref="AN92:AO92"/>
-    <mergeCell ref="AN93:AO93"/>
-    <mergeCell ref="AN94:AO94"/>
-    <mergeCell ref="AN95:AO95"/>
-    <mergeCell ref="AN96:AO96"/>
-    <mergeCell ref="AL72:AM72"/>
-    <mergeCell ref="AN72:AO72"/>
-    <mergeCell ref="AL73:AM73"/>
-    <mergeCell ref="AN73:AO73"/>
-    <mergeCell ref="AL74:AM74"/>
-    <mergeCell ref="AN74:AO74"/>
-    <mergeCell ref="AN75:AO75"/>
-    <mergeCell ref="AL75:AM75"/>
-    <mergeCell ref="X58:Y58"/>
-    <mergeCell ref="X59:Y59"/>
-    <mergeCell ref="X60:Y60"/>
-    <mergeCell ref="X61:Y61"/>
-    <mergeCell ref="X62:Y62"/>
-    <mergeCell ref="X63:Y63"/>
-    <mergeCell ref="X64:Y64"/>
-    <mergeCell ref="X65:Y65"/>
-    <mergeCell ref="X66:Y66"/>
-    <mergeCell ref="X49:Y49"/>
-    <mergeCell ref="X50:Y50"/>
-    <mergeCell ref="X51:Y51"/>
-    <mergeCell ref="X52:Y52"/>
-    <mergeCell ref="X53:Y53"/>
-    <mergeCell ref="X54:Y54"/>
-    <mergeCell ref="X55:Y55"/>
-    <mergeCell ref="X56:Y56"/>
-    <mergeCell ref="X57:Y57"/>
-    <mergeCell ref="X40:Y40"/>
-    <mergeCell ref="X41:Y41"/>
-    <mergeCell ref="X42:Y42"/>
-    <mergeCell ref="X43:Y43"/>
-    <mergeCell ref="X44:Y44"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="X46:Y46"/>
-    <mergeCell ref="X47:Y47"/>
-    <mergeCell ref="X48:Y48"/>
-    <mergeCell ref="X31:Y31"/>
-    <mergeCell ref="X32:Y32"/>
-    <mergeCell ref="X33:Y33"/>
-    <mergeCell ref="X34:Y34"/>
-    <mergeCell ref="X35:Y35"/>
-    <mergeCell ref="X36:Y36"/>
-    <mergeCell ref="X37:Y37"/>
-    <mergeCell ref="X38:Y38"/>
-    <mergeCell ref="X39:Y39"/>
-    <mergeCell ref="X25:Y25"/>
-    <mergeCell ref="AL24:AM24"/>
-    <mergeCell ref="AL25:AM25"/>
-    <mergeCell ref="X24:Y24"/>
-    <mergeCell ref="X26:Y26"/>
-    <mergeCell ref="X27:Y27"/>
-    <mergeCell ref="X28:Y28"/>
-    <mergeCell ref="X29:Y29"/>
-    <mergeCell ref="X30:Y30"/>
-    <mergeCell ref="AD28:AE28"/>
-    <mergeCell ref="AF28:AG28"/>
-    <mergeCell ref="AD29:AE29"/>
-    <mergeCell ref="AF29:AG29"/>
-    <mergeCell ref="AD30:AE30"/>
-    <mergeCell ref="AF30:AG30"/>
-    <mergeCell ref="AL28:AM28"/>
-    <mergeCell ref="AD16:AE16"/>
-    <mergeCell ref="AF16:AG16"/>
-    <mergeCell ref="X16:Y16"/>
-    <mergeCell ref="X17:Y17"/>
-    <mergeCell ref="X18:Y18"/>
-    <mergeCell ref="X19:Y19"/>
-    <mergeCell ref="X20:Y20"/>
-    <mergeCell ref="X21:Y21"/>
-    <mergeCell ref="X22:Y22"/>
-    <mergeCell ref="X13:Y13"/>
-    <mergeCell ref="AD13:AE13"/>
-    <mergeCell ref="AF13:AG13"/>
-    <mergeCell ref="AL13:AM13"/>
-    <mergeCell ref="AN13:AO13"/>
-    <mergeCell ref="X14:Y14"/>
-    <mergeCell ref="AD14:AE14"/>
-    <mergeCell ref="AF14:AG14"/>
-    <mergeCell ref="X15:Y15"/>
-    <mergeCell ref="AD15:AE15"/>
-    <mergeCell ref="AF15:AG15"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="J11:K11"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="R11:S11"/>
-    <mergeCell ref="T11:U11"/>
-    <mergeCell ref="AD11:AE11"/>
-    <mergeCell ref="AF11:AG11"/>
-    <mergeCell ref="AL11:AM11"/>
-    <mergeCell ref="AN11:AO11"/>
-    <mergeCell ref="X11:Y11"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="R4:S4"/>
-    <mergeCell ref="E7:G7"/>
-    <mergeCell ref="H7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="N7:P7"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="E9:G9"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="K9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="Q9:S9"/>
-    <mergeCell ref="AL21:AM21"/>
-    <mergeCell ref="AL22:AM22"/>
-    <mergeCell ref="AL20:AM20"/>
-    <mergeCell ref="AN20:AO20"/>
-    <mergeCell ref="AD21:AE21"/>
-    <mergeCell ref="AF21:AG21"/>
-    <mergeCell ref="AN21:AO21"/>
-    <mergeCell ref="AF22:AG22"/>
-    <mergeCell ref="AN22:AO22"/>
-    <mergeCell ref="AD22:AE22"/>
-    <mergeCell ref="AD115:AE115"/>
-    <mergeCell ref="AF115:AG115"/>
-    <mergeCell ref="AD116:AE116"/>
-    <mergeCell ref="AF116:AG116"/>
-    <mergeCell ref="AL17:AM17"/>
-    <mergeCell ref="AL18:AM18"/>
-    <mergeCell ref="AL14:AM14"/>
-    <mergeCell ref="AN14:AO14"/>
-    <mergeCell ref="AL15:AM15"/>
-    <mergeCell ref="AN15:AO15"/>
-    <mergeCell ref="AL16:AM16"/>
-    <mergeCell ref="AN16:AO16"/>
-    <mergeCell ref="AN17:AO17"/>
-    <mergeCell ref="AN18:AO18"/>
-    <mergeCell ref="AD19:AE19"/>
-    <mergeCell ref="AD20:AE20"/>
-    <mergeCell ref="AF20:AG20"/>
-    <mergeCell ref="AD17:AE17"/>
-    <mergeCell ref="AF17:AG17"/>
-    <mergeCell ref="AD18:AE18"/>
-    <mergeCell ref="AF18:AG18"/>
-    <mergeCell ref="AF19:AG19"/>
-    <mergeCell ref="AL19:AM19"/>
-    <mergeCell ref="AN19:AO19"/>
-    <mergeCell ref="X94:Y94"/>
-    <mergeCell ref="AD90:AE90"/>
-    <mergeCell ref="AD91:AE91"/>
-    <mergeCell ref="AD92:AE92"/>
-    <mergeCell ref="AD93:AE93"/>
-    <mergeCell ref="AD94:AE94"/>
-    <mergeCell ref="AD95:AE95"/>
-    <mergeCell ref="AD96:AE96"/>
-    <mergeCell ref="AD105:AE105"/>
-    <mergeCell ref="AD103:AE103"/>
-    <mergeCell ref="AD97:AE97"/>
-    <mergeCell ref="AD98:AE98"/>
-    <mergeCell ref="AD99:AE99"/>
-    <mergeCell ref="AD100:AE100"/>
-    <mergeCell ref="X95:Y95"/>
-    <mergeCell ref="X96:Y96"/>
-    <mergeCell ref="X97:Y97"/>
-    <mergeCell ref="X98:Y98"/>
-    <mergeCell ref="X99:Y99"/>
-    <mergeCell ref="X100:Y100"/>
-    <mergeCell ref="X101:Y101"/>
-    <mergeCell ref="X102:Y102"/>
-    <mergeCell ref="X103:Y103"/>
-    <mergeCell ref="AD89:AE89"/>
-    <mergeCell ref="AF89:AG89"/>
-    <mergeCell ref="AF90:AG90"/>
-    <mergeCell ref="X88:Y88"/>
-    <mergeCell ref="X89:Y89"/>
-    <mergeCell ref="X90:Y90"/>
-    <mergeCell ref="X91:Y91"/>
-    <mergeCell ref="X92:Y92"/>
-    <mergeCell ref="X93:Y93"/>
-    <mergeCell ref="X83:Y83"/>
-    <mergeCell ref="X84:Y84"/>
-    <mergeCell ref="X85:Y85"/>
-    <mergeCell ref="X86:Y86"/>
-    <mergeCell ref="X87:Y87"/>
-    <mergeCell ref="AD87:AE87"/>
-    <mergeCell ref="AF87:AG87"/>
-    <mergeCell ref="AD88:AE88"/>
-    <mergeCell ref="AF88:AG88"/>
-    <mergeCell ref="AD84:AE84"/>
-    <mergeCell ref="AD85:AE85"/>
-    <mergeCell ref="AD86:AE86"/>
-    <mergeCell ref="X74:Y74"/>
-    <mergeCell ref="X75:Y75"/>
-    <mergeCell ref="X76:Y76"/>
-    <mergeCell ref="X77:Y77"/>
-    <mergeCell ref="X78:Y78"/>
-    <mergeCell ref="X79:Y79"/>
-    <mergeCell ref="X80:Y80"/>
-    <mergeCell ref="X81:Y81"/>
-    <mergeCell ref="X82:Y82"/>
-    <mergeCell ref="AD120:AE120"/>
-    <mergeCell ref="AD121:AE121"/>
-    <mergeCell ref="AD122:AE122"/>
-    <mergeCell ref="AF121:AG121"/>
-    <mergeCell ref="AF122:AG122"/>
-    <mergeCell ref="AD117:AE117"/>
-    <mergeCell ref="AF117:AG117"/>
-    <mergeCell ref="AD118:AE118"/>
-    <mergeCell ref="AF118:AG118"/>
-    <mergeCell ref="AD119:AE119"/>
-    <mergeCell ref="AF119:AG119"/>
-    <mergeCell ref="AF120:AG120"/>
-    <mergeCell ref="AF103:AG103"/>
-    <mergeCell ref="AD104:AE104"/>
-    <mergeCell ref="AF104:AG104"/>
-    <mergeCell ref="AF105:AG105"/>
-    <mergeCell ref="AF113:AG113"/>
-    <mergeCell ref="AF114:AG114"/>
-    <mergeCell ref="AF106:AG106"/>
-    <mergeCell ref="AF107:AG107"/>
-    <mergeCell ref="AF108:AG108"/>
-    <mergeCell ref="AF109:AG109"/>
-    <mergeCell ref="AF110:AG110"/>
-    <mergeCell ref="AF111:AG111"/>
-    <mergeCell ref="AF112:AG112"/>
-    <mergeCell ref="AD106:AE106"/>
-    <mergeCell ref="AD107:AE107"/>
-    <mergeCell ref="AD108:AE108"/>
-    <mergeCell ref="AD109:AE109"/>
-    <mergeCell ref="AD110:AE110"/>
-    <mergeCell ref="AD111:AE111"/>
-    <mergeCell ref="AD112:AE112"/>
-    <mergeCell ref="AD113:AE113"/>
-    <mergeCell ref="AD114:AE114"/>
-    <mergeCell ref="AF100:AG100"/>
-    <mergeCell ref="AD101:AE101"/>
-    <mergeCell ref="AF101:AG101"/>
-    <mergeCell ref="AD102:AE102"/>
-    <mergeCell ref="AF102:AG102"/>
-    <mergeCell ref="X120:Y120"/>
-    <mergeCell ref="X121:Y121"/>
-    <mergeCell ref="X122:Y122"/>
-    <mergeCell ref="X109:Y109"/>
-    <mergeCell ref="X110:Y110"/>
-    <mergeCell ref="X111:Y111"/>
-    <mergeCell ref="X112:Y112"/>
-    <mergeCell ref="X113:Y113"/>
-    <mergeCell ref="X114:Y114"/>
-    <mergeCell ref="X115:Y115"/>
-    <mergeCell ref="X104:Y104"/>
-    <mergeCell ref="X105:Y105"/>
-    <mergeCell ref="X106:Y106"/>
-    <mergeCell ref="X107:Y107"/>
-    <mergeCell ref="X108:Y108"/>
-    <mergeCell ref="X116:Y116"/>
-    <mergeCell ref="X117:Y117"/>
-    <mergeCell ref="X118:Y118"/>
-    <mergeCell ref="X119:Y119"/>
-    <mergeCell ref="AF98:AG98"/>
-    <mergeCell ref="AF99:AG99"/>
-    <mergeCell ref="AF91:AG91"/>
-    <mergeCell ref="AF92:AG92"/>
-    <mergeCell ref="AF93:AG93"/>
-    <mergeCell ref="AF94:AG94"/>
-    <mergeCell ref="AF95:AG95"/>
-    <mergeCell ref="AF96:AG96"/>
-    <mergeCell ref="AF97:AG97"/>
-    <mergeCell ref="AD77:AE77"/>
-    <mergeCell ref="AD78:AE78"/>
-    <mergeCell ref="AD79:AE79"/>
-    <mergeCell ref="AD80:AE80"/>
-    <mergeCell ref="AD81:AE81"/>
-    <mergeCell ref="AD82:AE82"/>
-    <mergeCell ref="AD83:AE83"/>
-    <mergeCell ref="AD70:AE70"/>
-    <mergeCell ref="AD71:AE71"/>
-    <mergeCell ref="AD72:AE72"/>
-    <mergeCell ref="AD73:AE73"/>
-    <mergeCell ref="AD74:AE74"/>
-    <mergeCell ref="AD75:AE75"/>
-    <mergeCell ref="AD76:AE76"/>
-    <mergeCell ref="AF71:AG71"/>
-    <mergeCell ref="AF72:AG72"/>
-    <mergeCell ref="AF73:AG73"/>
-    <mergeCell ref="AF74:AG74"/>
-    <mergeCell ref="AF75:AG75"/>
-    <mergeCell ref="AF76:AG76"/>
-    <mergeCell ref="AD65:AE65"/>
-    <mergeCell ref="AD66:AE66"/>
-    <mergeCell ref="AD67:AE67"/>
-    <mergeCell ref="AD68:AE68"/>
-    <mergeCell ref="AD69:AE69"/>
-    <mergeCell ref="AF64:AG64"/>
-    <mergeCell ref="AF65:AG65"/>
-    <mergeCell ref="AF66:AG66"/>
-    <mergeCell ref="AF67:AG67"/>
-    <mergeCell ref="AF68:AG68"/>
-    <mergeCell ref="AF69:AG69"/>
-    <mergeCell ref="AD60:AE60"/>
-    <mergeCell ref="AF60:AG60"/>
-    <mergeCell ref="AD61:AE61"/>
-    <mergeCell ref="AF61:AG61"/>
-    <mergeCell ref="AD62:AE62"/>
-    <mergeCell ref="AF62:AG62"/>
-    <mergeCell ref="AF63:AG63"/>
-    <mergeCell ref="AD63:AE63"/>
-    <mergeCell ref="AD64:AE64"/>
-    <mergeCell ref="AL69:AM69"/>
-    <mergeCell ref="AL70:AM70"/>
-    <mergeCell ref="AN70:AO70"/>
-    <mergeCell ref="AL71:AM71"/>
-    <mergeCell ref="AN71:AO71"/>
-    <mergeCell ref="AF85:AG85"/>
-    <mergeCell ref="AF86:AG86"/>
-    <mergeCell ref="AF78:AG78"/>
-    <mergeCell ref="AF79:AG79"/>
-    <mergeCell ref="AF80:AG80"/>
-    <mergeCell ref="AF81:AG81"/>
-    <mergeCell ref="AF82:AG82"/>
-    <mergeCell ref="AF83:AG83"/>
-    <mergeCell ref="AF84:AG84"/>
-    <mergeCell ref="AF70:AG70"/>
-    <mergeCell ref="AF77:AG77"/>
-    <mergeCell ref="AL76:AM76"/>
-    <mergeCell ref="AL77:AM77"/>
-    <mergeCell ref="AL78:AM78"/>
-    <mergeCell ref="AL79:AM79"/>
-    <mergeCell ref="AL80:AM80"/>
-    <mergeCell ref="AL81:AM81"/>
-    <mergeCell ref="AN76:AO76"/>
-    <mergeCell ref="AN77:AO77"/>
-    <mergeCell ref="AN53:AO53"/>
-    <mergeCell ref="AL53:AM53"/>
-    <mergeCell ref="AL54:AM54"/>
-    <mergeCell ref="AL55:AM55"/>
-    <mergeCell ref="AL56:AM56"/>
-    <mergeCell ref="AL57:AM57"/>
-    <mergeCell ref="AL58:AM58"/>
-    <mergeCell ref="AL59:AM59"/>
-    <mergeCell ref="AN54:AO54"/>
-    <mergeCell ref="AN55:AO55"/>
-    <mergeCell ref="AN56:AO56"/>
-    <mergeCell ref="AN57:AO57"/>
-    <mergeCell ref="AN58:AO58"/>
-    <mergeCell ref="AN59:AO59"/>
-    <mergeCell ref="AL48:AM48"/>
-    <mergeCell ref="AL49:AM49"/>
-    <mergeCell ref="AL50:AM50"/>
-    <mergeCell ref="AL51:AM51"/>
-    <mergeCell ref="AL52:AM52"/>
-    <mergeCell ref="AN47:AO47"/>
-    <mergeCell ref="AN48:AO48"/>
-    <mergeCell ref="AN49:AO49"/>
-    <mergeCell ref="AN50:AO50"/>
-    <mergeCell ref="AN51:AO51"/>
-    <mergeCell ref="AN52:AO52"/>
-    <mergeCell ref="AD57:AE57"/>
-    <mergeCell ref="AD58:AE58"/>
-    <mergeCell ref="AF58:AG58"/>
-    <mergeCell ref="AD59:AE59"/>
-    <mergeCell ref="AF59:AG59"/>
-    <mergeCell ref="AN68:AO68"/>
-    <mergeCell ref="AN69:AO69"/>
-    <mergeCell ref="AN61:AO61"/>
-    <mergeCell ref="AN62:AO62"/>
-    <mergeCell ref="AN63:AO63"/>
-    <mergeCell ref="AN64:AO64"/>
-    <mergeCell ref="AN65:AO65"/>
-    <mergeCell ref="AN66:AO66"/>
-    <mergeCell ref="AN67:AO67"/>
-    <mergeCell ref="AN60:AO60"/>
-    <mergeCell ref="AL60:AM60"/>
-    <mergeCell ref="AL61:AM61"/>
-    <mergeCell ref="AL62:AM62"/>
-    <mergeCell ref="AL63:AM63"/>
-    <mergeCell ref="AL64:AM64"/>
-    <mergeCell ref="AL65:AM65"/>
-    <mergeCell ref="AL66:AM66"/>
-    <mergeCell ref="AL67:AM67"/>
-    <mergeCell ref="AL68:AM68"/>
-    <mergeCell ref="AD48:AE48"/>
-    <mergeCell ref="AD49:AE49"/>
-    <mergeCell ref="AD50:AE50"/>
-    <mergeCell ref="AD51:AE51"/>
-    <mergeCell ref="AD52:AE52"/>
-    <mergeCell ref="AD53:AE53"/>
-    <mergeCell ref="AD54:AE54"/>
-    <mergeCell ref="AD55:AE55"/>
-    <mergeCell ref="AD56:AE56"/>
-    <mergeCell ref="AD43:AE43"/>
-    <mergeCell ref="AD44:AE44"/>
-    <mergeCell ref="AD45:AE45"/>
-    <mergeCell ref="AD46:AE46"/>
-    <mergeCell ref="AD47:AE47"/>
-    <mergeCell ref="AF42:AG42"/>
-    <mergeCell ref="AF43:AG43"/>
-    <mergeCell ref="AF44:AG44"/>
-    <mergeCell ref="AF45:AG45"/>
-    <mergeCell ref="AF46:AG46"/>
-    <mergeCell ref="AF47:AG47"/>
-    <mergeCell ref="AD40:AE40"/>
-    <mergeCell ref="AF35:AG35"/>
-    <mergeCell ref="AF36:AG36"/>
-    <mergeCell ref="AF37:AG37"/>
-    <mergeCell ref="AF38:AG38"/>
-    <mergeCell ref="AF39:AG39"/>
-    <mergeCell ref="AF40:AG40"/>
-    <mergeCell ref="AD41:AE41"/>
-    <mergeCell ref="AD42:AE42"/>
-    <mergeCell ref="AD33:AE33"/>
-    <mergeCell ref="AF33:AG33"/>
-    <mergeCell ref="AF34:AG34"/>
-    <mergeCell ref="AD34:AE34"/>
-    <mergeCell ref="AD35:AE35"/>
-    <mergeCell ref="AD36:AE36"/>
-    <mergeCell ref="AD37:AE37"/>
-    <mergeCell ref="AD38:AE38"/>
-    <mergeCell ref="AD39:AE39"/>
-    <mergeCell ref="AL41:AM41"/>
-    <mergeCell ref="AN41:AO41"/>
-    <mergeCell ref="AL42:AM42"/>
-    <mergeCell ref="AN42:AO42"/>
-    <mergeCell ref="AF56:AG56"/>
-    <mergeCell ref="AF57:AG57"/>
-    <mergeCell ref="AF49:AG49"/>
-    <mergeCell ref="AF50:AG50"/>
-    <mergeCell ref="AF51:AG51"/>
-    <mergeCell ref="AF52:AG52"/>
-    <mergeCell ref="AF53:AG53"/>
-    <mergeCell ref="AF54:AG54"/>
-    <mergeCell ref="AF55:AG55"/>
-    <mergeCell ref="AF41:AG41"/>
-    <mergeCell ref="AF48:AG48"/>
-    <mergeCell ref="AL43:AM43"/>
-    <mergeCell ref="AN43:AO43"/>
-    <mergeCell ref="AL44:AM44"/>
-    <mergeCell ref="AN44:AO44"/>
-    <mergeCell ref="AL45:AM45"/>
-    <mergeCell ref="AN45:AO45"/>
-    <mergeCell ref="AN46:AO46"/>
-    <mergeCell ref="AL46:AM46"/>
-    <mergeCell ref="AL47:AM47"/>
-    <mergeCell ref="X23:Y23"/>
-    <mergeCell ref="AD24:AE24"/>
-    <mergeCell ref="AF24:AG24"/>
-    <mergeCell ref="AN24:AO24"/>
-    <mergeCell ref="AN39:AO39"/>
-    <mergeCell ref="AN28:AO28"/>
-    <mergeCell ref="AL29:AM29"/>
-    <mergeCell ref="AN29:AO29"/>
-    <mergeCell ref="AL30:AM30"/>
-    <mergeCell ref="AN30:AO30"/>
-    <mergeCell ref="AD25:AE25"/>
-    <mergeCell ref="AF25:AG25"/>
-    <mergeCell ref="AN25:AO25"/>
-    <mergeCell ref="AD26:AE26"/>
-    <mergeCell ref="AF26:AG26"/>
-    <mergeCell ref="AL26:AM26"/>
-    <mergeCell ref="AN26:AO26"/>
-    <mergeCell ref="AF27:AG27"/>
-    <mergeCell ref="AL27:AM27"/>
-    <mergeCell ref="AN27:AO27"/>
-    <mergeCell ref="AD27:AE27"/>
-    <mergeCell ref="AN31:AO31"/>
-    <mergeCell ref="AL31:AM31"/>
-    <mergeCell ref="AL32:AM32"/>
-    <mergeCell ref="AN40:AO40"/>
-    <mergeCell ref="AN32:AO32"/>
-    <mergeCell ref="AN33:AO33"/>
-    <mergeCell ref="AN34:AO34"/>
-    <mergeCell ref="AN35:AO35"/>
-    <mergeCell ref="AN36:AO36"/>
-    <mergeCell ref="AN37:AO37"/>
-    <mergeCell ref="AN38:AO38"/>
-    <mergeCell ref="AD23:AE23"/>
-    <mergeCell ref="AF23:AG23"/>
-    <mergeCell ref="AL23:AM23"/>
-    <mergeCell ref="AN23:AO23"/>
-    <mergeCell ref="AL33:AM33"/>
-    <mergeCell ref="AL34:AM34"/>
-    <mergeCell ref="AL35:AM35"/>
-    <mergeCell ref="AL36:AM36"/>
-    <mergeCell ref="AL37:AM37"/>
-    <mergeCell ref="AL38:AM38"/>
-    <mergeCell ref="AL39:AM39"/>
-    <mergeCell ref="AL40:AM40"/>
-    <mergeCell ref="AD31:AE31"/>
-    <mergeCell ref="AF31:AG31"/>
-    <mergeCell ref="AD32:AE32"/>
-    <mergeCell ref="AF32:AG32"/>
+    <mergeCell ref="AN78:AO78"/>
+    <mergeCell ref="AN79:AO79"/>
+    <mergeCell ref="AN80:AO80"/>
+    <mergeCell ref="AN81:AO81"/>
+    <mergeCell ref="AN82:AO82"/>
+    <mergeCell ref="AL82:AM82"/>
+    <mergeCell ref="AL83:AM83"/>
+    <mergeCell ref="AL84:AM84"/>
+    <mergeCell ref="AL85:AM85"/>
+    <mergeCell ref="AL86:AM86"/>
+    <mergeCell ref="AL87:AM87"/>
+    <mergeCell ref="AL88:AM88"/>
+    <mergeCell ref="AN83:AO83"/>
+    <mergeCell ref="AN84:AO84"/>
+    <mergeCell ref="AN85:AO85"/>
+    <mergeCell ref="AN86:AO86"/>
+    <mergeCell ref="AN87:AO87"/>
+    <mergeCell ref="AN88:AO88"/>
+    <mergeCell ref="AL97:AM97"/>
+    <mergeCell ref="AL98:AM98"/>
+    <mergeCell ref="AL99:AM99"/>
+    <mergeCell ref="AN99:AO99"/>
+    <mergeCell ref="AL100:AM100"/>
+    <mergeCell ref="AN100:AO100"/>
+    <mergeCell ref="AN89:AO89"/>
+    <mergeCell ref="AL89:AM89"/>
+    <mergeCell ref="AL90:AM90"/>
+    <mergeCell ref="AL91:AM91"/>
+    <mergeCell ref="AL92:AM92"/>
+    <mergeCell ref="AL93:AM93"/>
+    <mergeCell ref="AL94:AM94"/>
+    <mergeCell ref="AL95:AM95"/>
+    <mergeCell ref="AL96:AM96"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="R4" xr:uid="{00000000-0002-0000-0000-000000000000}">
